--- a/file/table/BogotaRiverLevels_HECRAS_Parameters.xlsx
+++ b/file/table/BogotaRiverLevels_HECRAS_Parameters.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.WREM\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A2D14FF-C04E-472E-A479-83862BEE2052}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D845259-A5AE-4F93-89A8-160276FDBAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="20666" windowHeight="12266" xr2:uid="{2255F479-0D41-4B39-BE5A-1B1436E09AAA}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="20666" windowHeight="12266" firstSheet="2" activeTab="4" xr2:uid="{2255F479-0D41-4B39-BE5A-1B1436E09AAA}"/>
   </bookViews>
   <sheets>
     <sheet name="21208110_21209770 " sheetId="1" r:id="rId1"/>
     <sheet name="HECRAS_Prototype1D_v0" sheetId="3" r:id="rId2"/>
     <sheet name="HECRAS_Prototype2D_v0" sheetId="4" r:id="rId3"/>
     <sheet name="Metadata" sheetId="2" r:id="rId4"/>
+    <sheet name="HECRAS_River_v0" sheetId="5" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="58">
   <si>
     <t>Date</t>
   </si>
@@ -207,6 +208,12 @@
   </si>
   <si>
     <t>https://github.com/rcfdtools/rcfdtools/blob/main/tool/ynyc/Readme.md</t>
+  </si>
+  <si>
+    <t>Time to peak: xxx hr</t>
+  </si>
+  <si>
+    <t>HEC-RAS 2D</t>
   </si>
 </sst>
 </file>
@@ -2391,7 +2398,7 @@
         <v>8</v>
       </c>
       <c r="J3" s="23" t="str">
-        <f>_xlfn.CONCAT(B3,": ",C3)</f>
+        <f t="shared" ref="J3:J22" si="0">_xlfn.CONCAT(B3,": ",C3)</f>
         <v>Parámetro: Valor</v>
       </c>
     </row>
@@ -2403,7 +2410,7 @@
         <v>37</v>
       </c>
       <c r="J4" s="23" t="str">
-        <f>_xlfn.CONCAT(B4,": ",C4)</f>
+        <f t="shared" si="0"/>
         <v>Estación: PTE LA VIRGEN  [21208110], PTE LA VIRGEN  [21209770]</v>
       </c>
     </row>
@@ -2415,7 +2422,7 @@
         <v>140</v>
       </c>
       <c r="J5" s="23" t="str">
-        <f>_xlfn.CONCAT(B5,": ",C5)</f>
+        <f t="shared" si="0"/>
         <v>Q, caudal (m³/s): 140</v>
       </c>
     </row>
@@ -2427,7 +2434,7 @@
         <v>500</v>
       </c>
       <c r="J6" s="23" t="str">
-        <f>_xlfn.CONCAT(B6,": ",C6)</f>
+        <f t="shared" si="0"/>
         <v>L, longitud canal (m): 500</v>
       </c>
     </row>
@@ -2439,7 +2446,7 @@
         <v>50</v>
       </c>
       <c r="J7" s="23" t="str">
-        <f>_xlfn.CONCAT(B7,": ",C7)</f>
+        <f t="shared" si="0"/>
         <v>T, ancho corona (m): 50</v>
       </c>
     </row>
@@ -2451,7 +2458,7 @@
         <v>26</v>
       </c>
       <c r="J8" s="23" t="str">
-        <f>_xlfn.CONCAT(B8,": ",C8)</f>
+        <f t="shared" si="0"/>
         <v>b, base canal (m): 26</v>
       </c>
     </row>
@@ -2463,7 +2470,7 @@
         <v>2</v>
       </c>
       <c r="J9" s="23" t="str">
-        <f>_xlfn.CONCAT(B9,": ",C9)</f>
+        <f t="shared" si="0"/>
         <v>z1, Talud izquierdo (z:1): 2</v>
       </c>
     </row>
@@ -2475,7 +2482,7 @@
         <v>2</v>
       </c>
       <c r="J10" s="23" t="str">
-        <f>_xlfn.CONCAT(B10,": ",C10)</f>
+        <f t="shared" si="0"/>
         <v>z2, Talud derecho (z:1): 2</v>
       </c>
     </row>
@@ -2487,7 +2494,7 @@
         <v>3.5000000000000003E-2</v>
       </c>
       <c r="J11" s="23" t="str">
-        <f>_xlfn.CONCAT(B11,": ",C11)</f>
+        <f t="shared" si="0"/>
         <v>n Manning canal ppal: 0.035</v>
       </c>
     </row>
@@ -2499,7 +2506,7 @@
         <v>0.05</v>
       </c>
       <c r="J12" s="23" t="str">
-        <f>_xlfn.CONCAT(B12,": ",C12)</f>
+        <f t="shared" si="0"/>
         <v>n Manning bancas: 0.05</v>
       </c>
     </row>
@@ -2511,7 +2518,7 @@
         <v>0.06</v>
       </c>
       <c r="J13" s="23" t="str">
-        <f>_xlfn.CONCAT(B13,": ",C13)</f>
+        <f t="shared" si="0"/>
         <v>n Manning llanura: 0.06</v>
       </c>
     </row>
@@ -2523,7 +2530,7 @@
         <v>6.9999999999999994E-5</v>
       </c>
       <c r="J14" s="23" t="str">
-        <f>_xlfn.CONCAT(B14,": ",C14)</f>
+        <f t="shared" si="0"/>
         <v>s, pendiente (m/m): 0.00007</v>
       </c>
     </row>
@@ -2535,7 +2542,7 @@
         <v>1.1424E-2</v>
       </c>
       <c r="J15" s="23" t="str">
-        <f>_xlfn.CONCAT(B15,": ",C15)</f>
+        <f t="shared" si="0"/>
         <v>s, pendiente crítica (m/m): 0.011424</v>
       </c>
     </row>
@@ -2547,7 +2554,7 @@
         <v>4878523</v>
       </c>
       <c r="J16" s="23" t="str">
-        <f>_xlfn.CONCAT(B16,": ",C16)</f>
+        <f t="shared" si="0"/>
         <v>CX (m): 4878523</v>
       </c>
     </row>
@@ -2559,7 +2566,7 @@
         <v>2088408</v>
       </c>
       <c r="J17" s="23" t="str">
-        <f>_xlfn.CONCAT(B17,": ",C17)</f>
+        <f t="shared" si="0"/>
         <v>CY (m): 2088408</v>
       </c>
     </row>
@@ -2571,7 +2578,7 @@
         <v>2539.84</v>
       </c>
       <c r="J18" s="23" t="str">
-        <f>_xlfn.CONCAT(B18,": ",C18)</f>
+        <f t="shared" si="0"/>
         <v>Cero Limnímetro (m): 2539.84</v>
       </c>
     </row>
@@ -2583,7 +2590,7 @@
         <v>2545.71</v>
       </c>
       <c r="J19" s="23" t="str">
-        <f>_xlfn.CONCAT(B19,": ",C19)</f>
+        <f t="shared" si="0"/>
         <v>Cota Jarillón Izq. (m): 2545.71</v>
       </c>
     </row>
@@ -2596,7 +2603,7 @@
       </c>
       <c r="E20" s="4"/>
       <c r="J20" s="23" t="str">
-        <f>_xlfn.CONCAT(B20,": ",C20)</f>
+        <f t="shared" si="0"/>
         <v>Cota Jarillón Der. (m): 2546.77</v>
       </c>
     </row>
@@ -2610,7 +2617,7 @@
       </c>
       <c r="E21" s="3"/>
       <c r="J21" s="23" t="str">
-        <f>_xlfn.CONCAT(B21,": ",C21)</f>
+        <f t="shared" si="0"/>
         <v>Alto Jarillón Izq. (m): 5.86999999999989</v>
       </c>
     </row>
@@ -2624,7 +2631,7 @@
       </c>
       <c r="E22" s="3"/>
       <c r="J22" s="23" t="str">
-        <f>_xlfn.CONCAT(B22,": ",C22)</f>
+        <f t="shared" si="0"/>
         <v>Alto Jarillón Der. (m): 6.92999999999984</v>
       </c>
     </row>
@@ -8706,4 +8713,2485 @@
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{150C82D4-B0A3-45ED-9F3F-D11EA85F382E}">
+  <dimension ref="B2:D228"/>
+  <sheetFormatPr defaultRowHeight="16.350000000000001" x14ac:dyDescent="0.5"/>
+  <cols>
+    <col min="1" max="1" width="2.64453125" style="9" customWidth="1"/>
+    <col min="2" max="3" width="17.76171875" style="9" customWidth="1"/>
+    <col min="4" max="4" width="16.234375" style="9" customWidth="1"/>
+    <col min="5" max="16384" width="8.9375" style="9"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B2" s="9" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="3" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B3" s="9" t="s">
+        <v>49</v>
+      </c>
+      <c r="C3" s="9">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="5" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B5" s="9" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B6" s="9" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="7" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B7" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="C7" s="9" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B8" s="9">
+        <v>0</v>
+      </c>
+      <c r="C8" s="9">
+        <v>0</v>
+      </c>
+      <c r="D8" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B9" s="9">
+        <v>1</v>
+      </c>
+      <c r="C9" s="9">
+        <v>0.25</v>
+      </c>
+      <c r="D9" s="9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B10" s="9">
+        <v>2</v>
+      </c>
+      <c r="C10" s="9">
+        <v>0.5</v>
+      </c>
+      <c r="D10" s="9">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="11" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B11" s="9">
+        <v>3</v>
+      </c>
+      <c r="C11" s="9">
+        <v>0.75</v>
+      </c>
+      <c r="D11" s="9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="12" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B12" s="9">
+        <v>4</v>
+      </c>
+      <c r="C12" s="9">
+        <v>1</v>
+      </c>
+      <c r="D12" s="9">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B13" s="9">
+        <v>5</v>
+      </c>
+      <c r="C13" s="9">
+        <v>1.25</v>
+      </c>
+      <c r="D13" s="9">
+        <v>87.5</v>
+      </c>
+    </row>
+    <row r="14" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B14" s="9">
+        <v>6</v>
+      </c>
+      <c r="C14" s="9">
+        <v>1.5</v>
+      </c>
+      <c r="D14" s="9">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="15" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B15" s="9">
+        <v>7</v>
+      </c>
+      <c r="C15" s="9">
+        <v>1.75</v>
+      </c>
+      <c r="D15" s="9">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="16" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B16" s="9">
+        <v>8</v>
+      </c>
+      <c r="C16" s="9">
+        <v>2</v>
+      </c>
+      <c r="D16" s="9">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="17" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B17" s="9">
+        <v>9</v>
+      </c>
+      <c r="C17" s="9">
+        <v>2.25</v>
+      </c>
+      <c r="D17" s="9">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="18" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B18" s="9">
+        <v>10</v>
+      </c>
+      <c r="C18" s="9">
+        <v>2.5</v>
+      </c>
+      <c r="D18" s="9">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B19" s="9">
+        <v>11</v>
+      </c>
+      <c r="C19" s="9">
+        <v>2.75</v>
+      </c>
+      <c r="D19" s="9">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="20" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B20" s="9">
+        <v>12</v>
+      </c>
+      <c r="C20" s="9">
+        <v>3</v>
+      </c>
+      <c r="D20" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B21" s="9">
+        <v>13</v>
+      </c>
+      <c r="C21" s="9">
+        <v>3.25</v>
+      </c>
+      <c r="D21" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B22" s="9">
+        <v>14</v>
+      </c>
+      <c r="C22" s="9">
+        <v>3.5</v>
+      </c>
+      <c r="D22" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B23" s="9">
+        <v>15</v>
+      </c>
+      <c r="C23" s="9">
+        <v>3.75</v>
+      </c>
+      <c r="D23" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B24" s="9">
+        <v>16</v>
+      </c>
+      <c r="C24" s="9">
+        <v>4</v>
+      </c>
+      <c r="D24" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B25" s="9">
+        <v>17</v>
+      </c>
+      <c r="C25" s="9">
+        <v>4.25</v>
+      </c>
+      <c r="D25" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B26" s="9">
+        <v>18</v>
+      </c>
+      <c r="C26" s="9">
+        <v>4.5</v>
+      </c>
+      <c r="D26" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B27" s="9">
+        <v>19</v>
+      </c>
+      <c r="C27" s="9">
+        <v>4.75</v>
+      </c>
+      <c r="D27" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B28" s="9">
+        <v>20</v>
+      </c>
+      <c r="C28" s="9">
+        <v>5</v>
+      </c>
+      <c r="D28" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B29" s="9">
+        <v>21</v>
+      </c>
+      <c r="C29" s="9">
+        <v>5.25</v>
+      </c>
+      <c r="D29" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B30" s="9">
+        <v>22</v>
+      </c>
+      <c r="C30" s="9">
+        <v>5.5</v>
+      </c>
+      <c r="D30" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B31" s="9">
+        <v>23</v>
+      </c>
+      <c r="C31" s="9">
+        <v>5.75</v>
+      </c>
+      <c r="D31" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B32" s="9">
+        <v>24</v>
+      </c>
+      <c r="C32" s="9">
+        <v>6</v>
+      </c>
+      <c r="D32" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B33" s="9">
+        <v>25</v>
+      </c>
+      <c r="C33" s="9">
+        <v>6.25</v>
+      </c>
+      <c r="D33" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B34" s="9">
+        <v>26</v>
+      </c>
+      <c r="C34" s="9">
+        <v>6.5</v>
+      </c>
+      <c r="D34" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B35" s="9">
+        <v>27</v>
+      </c>
+      <c r="C35" s="9">
+        <v>6.75</v>
+      </c>
+      <c r="D35" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B36" s="9">
+        <v>28</v>
+      </c>
+      <c r="C36" s="9">
+        <v>7</v>
+      </c>
+      <c r="D36" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B37" s="9">
+        <v>29</v>
+      </c>
+      <c r="C37" s="9">
+        <v>7.25</v>
+      </c>
+      <c r="D37" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B38" s="9">
+        <v>30</v>
+      </c>
+      <c r="C38" s="9">
+        <v>7.5</v>
+      </c>
+      <c r="D38" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B39" s="9">
+        <v>31</v>
+      </c>
+      <c r="C39" s="9">
+        <v>7.75</v>
+      </c>
+      <c r="D39" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B40" s="9">
+        <v>32</v>
+      </c>
+      <c r="C40" s="9">
+        <v>8</v>
+      </c>
+      <c r="D40" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B41" s="9">
+        <v>33</v>
+      </c>
+      <c r="C41" s="9">
+        <v>8.25</v>
+      </c>
+      <c r="D41" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B42" s="9">
+        <v>34</v>
+      </c>
+      <c r="C42" s="9">
+        <v>8.5</v>
+      </c>
+      <c r="D42" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B43" s="9">
+        <v>35</v>
+      </c>
+      <c r="C43" s="9">
+        <v>8.75</v>
+      </c>
+      <c r="D43" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B44" s="9">
+        <v>36</v>
+      </c>
+      <c r="C44" s="9">
+        <v>9</v>
+      </c>
+      <c r="D44" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B45" s="9">
+        <v>37</v>
+      </c>
+      <c r="C45" s="9">
+        <v>9.25</v>
+      </c>
+      <c r="D45" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B46" s="9">
+        <v>38</v>
+      </c>
+      <c r="C46" s="9">
+        <v>9.5</v>
+      </c>
+      <c r="D46" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B47" s="9">
+        <v>39</v>
+      </c>
+      <c r="C47" s="9">
+        <v>9.75</v>
+      </c>
+      <c r="D47" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B48" s="9">
+        <v>40</v>
+      </c>
+      <c r="C48" s="9">
+        <v>10</v>
+      </c>
+      <c r="D48" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B49" s="9">
+        <v>41</v>
+      </c>
+      <c r="C49" s="9">
+        <v>10.25</v>
+      </c>
+      <c r="D49" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B50" s="9">
+        <v>42</v>
+      </c>
+      <c r="C50" s="9">
+        <v>10.5</v>
+      </c>
+      <c r="D50" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B51" s="9">
+        <v>43</v>
+      </c>
+      <c r="C51" s="9">
+        <v>10.75</v>
+      </c>
+      <c r="D51" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B52" s="9">
+        <v>44</v>
+      </c>
+      <c r="C52" s="9">
+        <v>11</v>
+      </c>
+      <c r="D52" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B53" s="9">
+        <v>45</v>
+      </c>
+      <c r="C53" s="9">
+        <v>11.25</v>
+      </c>
+      <c r="D53" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B54" s="9">
+        <v>46</v>
+      </c>
+      <c r="C54" s="9">
+        <v>11.5</v>
+      </c>
+      <c r="D54" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B55" s="9">
+        <v>47</v>
+      </c>
+      <c r="C55" s="9">
+        <v>11.75</v>
+      </c>
+      <c r="D55" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B56" s="9">
+        <v>48</v>
+      </c>
+      <c r="C56" s="9">
+        <v>12</v>
+      </c>
+      <c r="D56" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B57" s="9">
+        <v>49</v>
+      </c>
+      <c r="C57" s="9">
+        <v>12.25</v>
+      </c>
+      <c r="D57" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B58" s="9">
+        <v>50</v>
+      </c>
+      <c r="C58" s="9">
+        <v>12.5</v>
+      </c>
+      <c r="D58" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B59" s="9">
+        <v>51</v>
+      </c>
+      <c r="C59" s="9">
+        <v>12.75</v>
+      </c>
+      <c r="D59" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B60" s="9">
+        <v>52</v>
+      </c>
+      <c r="C60" s="9">
+        <v>13</v>
+      </c>
+      <c r="D60" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B61" s="9">
+        <v>53</v>
+      </c>
+      <c r="C61" s="9">
+        <v>13.25</v>
+      </c>
+      <c r="D61" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B62" s="9">
+        <v>54</v>
+      </c>
+      <c r="C62" s="9">
+        <v>13.5</v>
+      </c>
+      <c r="D62" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B63" s="9">
+        <v>55</v>
+      </c>
+      <c r="C63" s="9">
+        <v>13.75</v>
+      </c>
+      <c r="D63" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B64" s="9">
+        <v>56</v>
+      </c>
+      <c r="C64" s="9">
+        <v>14</v>
+      </c>
+      <c r="D64" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B65" s="9">
+        <v>57</v>
+      </c>
+      <c r="C65" s="9">
+        <v>14.25</v>
+      </c>
+      <c r="D65" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B66" s="9">
+        <v>58</v>
+      </c>
+      <c r="C66" s="9">
+        <v>14.5</v>
+      </c>
+      <c r="D66" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B67" s="9">
+        <v>59</v>
+      </c>
+      <c r="C67" s="9">
+        <v>14.75</v>
+      </c>
+      <c r="D67" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B68" s="9">
+        <v>60</v>
+      </c>
+      <c r="C68" s="9">
+        <v>15</v>
+      </c>
+      <c r="D68" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B69" s="9">
+        <v>61</v>
+      </c>
+      <c r="C69" s="9">
+        <v>15.25</v>
+      </c>
+      <c r="D69" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B70" s="9">
+        <v>62</v>
+      </c>
+      <c r="C70" s="9">
+        <v>15.5</v>
+      </c>
+      <c r="D70" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B71" s="9">
+        <v>63</v>
+      </c>
+      <c r="C71" s="9">
+        <v>15.75</v>
+      </c>
+      <c r="D71" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B72" s="9">
+        <v>64</v>
+      </c>
+      <c r="C72" s="9">
+        <v>16</v>
+      </c>
+      <c r="D72" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B73" s="9">
+        <v>65</v>
+      </c>
+      <c r="C73" s="9">
+        <v>16.25</v>
+      </c>
+      <c r="D73" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B74" s="9">
+        <v>66</v>
+      </c>
+      <c r="C74" s="9">
+        <v>16.5</v>
+      </c>
+      <c r="D74" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B75" s="9">
+        <v>67</v>
+      </c>
+      <c r="C75" s="9">
+        <v>16.75</v>
+      </c>
+      <c r="D75" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B76" s="9">
+        <v>68</v>
+      </c>
+      <c r="C76" s="9">
+        <v>17</v>
+      </c>
+      <c r="D76" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B77" s="9">
+        <v>69</v>
+      </c>
+      <c r="C77" s="9">
+        <v>17.25</v>
+      </c>
+      <c r="D77" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B78" s="9">
+        <v>70</v>
+      </c>
+      <c r="C78" s="9">
+        <v>17.5</v>
+      </c>
+      <c r="D78" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B79" s="9">
+        <v>71</v>
+      </c>
+      <c r="C79" s="9">
+        <v>17.75</v>
+      </c>
+      <c r="D79" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B80" s="9">
+        <v>72</v>
+      </c>
+      <c r="C80" s="9">
+        <v>18</v>
+      </c>
+      <c r="D80" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B81" s="9">
+        <v>73</v>
+      </c>
+      <c r="C81" s="9">
+        <v>18.25</v>
+      </c>
+      <c r="D81" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B82" s="9">
+        <v>74</v>
+      </c>
+      <c r="C82" s="9">
+        <v>18.5</v>
+      </c>
+      <c r="D82" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B83" s="9">
+        <v>75</v>
+      </c>
+      <c r="C83" s="9">
+        <v>18.75</v>
+      </c>
+      <c r="D83" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B84" s="9">
+        <v>76</v>
+      </c>
+      <c r="C84" s="9">
+        <v>19</v>
+      </c>
+      <c r="D84" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B85" s="9">
+        <v>77</v>
+      </c>
+      <c r="C85" s="9">
+        <v>19.25</v>
+      </c>
+      <c r="D85" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B86" s="9">
+        <v>78</v>
+      </c>
+      <c r="C86" s="9">
+        <v>19.5</v>
+      </c>
+      <c r="D86" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B87" s="9">
+        <v>79</v>
+      </c>
+      <c r="C87" s="9">
+        <v>19.75</v>
+      </c>
+      <c r="D87" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B88" s="9">
+        <v>80</v>
+      </c>
+      <c r="C88" s="9">
+        <v>20</v>
+      </c>
+      <c r="D88" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B89" s="9">
+        <v>81</v>
+      </c>
+      <c r="C89" s="9">
+        <v>20.25</v>
+      </c>
+      <c r="D89" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B90" s="9">
+        <v>82</v>
+      </c>
+      <c r="C90" s="9">
+        <v>20.5</v>
+      </c>
+      <c r="D90" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B91" s="9">
+        <v>83</v>
+      </c>
+      <c r="C91" s="9">
+        <v>20.75</v>
+      </c>
+      <c r="D91" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B92" s="9">
+        <v>84</v>
+      </c>
+      <c r="C92" s="9">
+        <v>21</v>
+      </c>
+      <c r="D92" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B93" s="9">
+        <v>85</v>
+      </c>
+      <c r="C93" s="9">
+        <v>21.25</v>
+      </c>
+      <c r="D93" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B94" s="9">
+        <v>86</v>
+      </c>
+      <c r="C94" s="9">
+        <v>21.5</v>
+      </c>
+      <c r="D94" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B95" s="9">
+        <v>87</v>
+      </c>
+      <c r="C95" s="9">
+        <v>21.75</v>
+      </c>
+      <c r="D95" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B96" s="9">
+        <v>88</v>
+      </c>
+      <c r="C96" s="9">
+        <v>22</v>
+      </c>
+      <c r="D96" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B97" s="9">
+        <v>89</v>
+      </c>
+      <c r="C97" s="9">
+        <v>22.25</v>
+      </c>
+      <c r="D97" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B98" s="9">
+        <v>90</v>
+      </c>
+      <c r="C98" s="9">
+        <v>22.5</v>
+      </c>
+      <c r="D98" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B99" s="9">
+        <v>91</v>
+      </c>
+      <c r="C99" s="9">
+        <v>22.75</v>
+      </c>
+      <c r="D99" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B100" s="9">
+        <v>92</v>
+      </c>
+      <c r="C100" s="9">
+        <v>23</v>
+      </c>
+      <c r="D100" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B101" s="9">
+        <v>93</v>
+      </c>
+      <c r="C101" s="9">
+        <v>23.25</v>
+      </c>
+      <c r="D101" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B102" s="9">
+        <v>94</v>
+      </c>
+      <c r="C102" s="9">
+        <v>23.5</v>
+      </c>
+      <c r="D102" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B103" s="9">
+        <v>95</v>
+      </c>
+      <c r="C103" s="9">
+        <v>23.75</v>
+      </c>
+      <c r="D103" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B104" s="9">
+        <v>96</v>
+      </c>
+      <c r="C104" s="9">
+        <v>24</v>
+      </c>
+      <c r="D104" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B105" s="9">
+        <v>97</v>
+      </c>
+      <c r="C105" s="9">
+        <v>24.25</v>
+      </c>
+      <c r="D105" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B106" s="9">
+        <v>98</v>
+      </c>
+      <c r="C106" s="9">
+        <v>24.5</v>
+      </c>
+      <c r="D106" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B107" s="9">
+        <v>99</v>
+      </c>
+      <c r="C107" s="9">
+        <v>24.75</v>
+      </c>
+      <c r="D107" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B108" s="9">
+        <v>100</v>
+      </c>
+      <c r="C108" s="9">
+        <v>25</v>
+      </c>
+      <c r="D108" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B109" s="9">
+        <v>101</v>
+      </c>
+      <c r="C109" s="9">
+        <v>25.25</v>
+      </c>
+      <c r="D109" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B110" s="9">
+        <v>102</v>
+      </c>
+      <c r="C110" s="9">
+        <v>25.5</v>
+      </c>
+      <c r="D110" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B111" s="9">
+        <v>103</v>
+      </c>
+      <c r="C111" s="9">
+        <v>25.75</v>
+      </c>
+      <c r="D111" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B112" s="9">
+        <v>104</v>
+      </c>
+      <c r="C112" s="9">
+        <v>26</v>
+      </c>
+      <c r="D112" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B113" s="9">
+        <v>105</v>
+      </c>
+      <c r="C113" s="9">
+        <v>26.25</v>
+      </c>
+      <c r="D113" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B114" s="9">
+        <v>106</v>
+      </c>
+      <c r="C114" s="9">
+        <v>26.5</v>
+      </c>
+      <c r="D114" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B115" s="9">
+        <v>107</v>
+      </c>
+      <c r="C115" s="9">
+        <v>26.75</v>
+      </c>
+      <c r="D115" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B116" s="9">
+        <v>108</v>
+      </c>
+      <c r="C116" s="9">
+        <v>27</v>
+      </c>
+      <c r="D116" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B117" s="9">
+        <v>109</v>
+      </c>
+      <c r="C117" s="9">
+        <v>27.25</v>
+      </c>
+      <c r="D117" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B118" s="9">
+        <v>110</v>
+      </c>
+      <c r="C118" s="9">
+        <v>27.5</v>
+      </c>
+      <c r="D118" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B119" s="9">
+        <v>111</v>
+      </c>
+      <c r="C119" s="9">
+        <v>27.75</v>
+      </c>
+      <c r="D119" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B120" s="9">
+        <v>112</v>
+      </c>
+      <c r="C120" s="9">
+        <v>28</v>
+      </c>
+      <c r="D120" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B121" s="9">
+        <v>113</v>
+      </c>
+      <c r="C121" s="9">
+        <v>28.25</v>
+      </c>
+      <c r="D121" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B122" s="9">
+        <v>114</v>
+      </c>
+      <c r="C122" s="9">
+        <v>28.5</v>
+      </c>
+      <c r="D122" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B123" s="9">
+        <v>115</v>
+      </c>
+      <c r="C123" s="9">
+        <v>28.75</v>
+      </c>
+      <c r="D123" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B124" s="9">
+        <v>116</v>
+      </c>
+      <c r="C124" s="9">
+        <v>29</v>
+      </c>
+      <c r="D124" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B125" s="9">
+        <v>117</v>
+      </c>
+      <c r="C125" s="9">
+        <v>29.25</v>
+      </c>
+      <c r="D125" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B126" s="9">
+        <v>118</v>
+      </c>
+      <c r="C126" s="9">
+        <v>29.5</v>
+      </c>
+      <c r="D126" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B127" s="9">
+        <v>119</v>
+      </c>
+      <c r="C127" s="9">
+        <v>29.75</v>
+      </c>
+      <c r="D127" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B128" s="9">
+        <v>120</v>
+      </c>
+      <c r="C128" s="9">
+        <v>30</v>
+      </c>
+      <c r="D128" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B129" s="9">
+        <v>121</v>
+      </c>
+      <c r="C129" s="9">
+        <v>30.25</v>
+      </c>
+      <c r="D129" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B130" s="9">
+        <v>122</v>
+      </c>
+      <c r="C130" s="9">
+        <v>30.5</v>
+      </c>
+      <c r="D130" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B131" s="9">
+        <v>123</v>
+      </c>
+      <c r="C131" s="9">
+        <v>30.75</v>
+      </c>
+      <c r="D131" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B132" s="9">
+        <v>124</v>
+      </c>
+      <c r="C132" s="9">
+        <v>31</v>
+      </c>
+      <c r="D132" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B133" s="9">
+        <v>125</v>
+      </c>
+      <c r="C133" s="9">
+        <v>31.25</v>
+      </c>
+      <c r="D133" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B134" s="9">
+        <v>126</v>
+      </c>
+      <c r="C134" s="9">
+        <v>31.5</v>
+      </c>
+      <c r="D134" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B135" s="9">
+        <v>127</v>
+      </c>
+      <c r="C135" s="9">
+        <v>31.75</v>
+      </c>
+      <c r="D135" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B136" s="9">
+        <v>128</v>
+      </c>
+      <c r="C136" s="9">
+        <v>32</v>
+      </c>
+      <c r="D136" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B137" s="9">
+        <v>129</v>
+      </c>
+      <c r="C137" s="9">
+        <v>32.25</v>
+      </c>
+      <c r="D137" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B138" s="9">
+        <v>130</v>
+      </c>
+      <c r="C138" s="9">
+        <v>32.5</v>
+      </c>
+      <c r="D138" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B139" s="9">
+        <v>131</v>
+      </c>
+      <c r="C139" s="9">
+        <v>32.75</v>
+      </c>
+      <c r="D139" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B140" s="9">
+        <v>132</v>
+      </c>
+      <c r="C140" s="9">
+        <v>33</v>
+      </c>
+      <c r="D140" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B141" s="9">
+        <v>133</v>
+      </c>
+      <c r="C141" s="9">
+        <v>33.25</v>
+      </c>
+      <c r="D141" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B142" s="9">
+        <v>134</v>
+      </c>
+      <c r="C142" s="9">
+        <v>33.5</v>
+      </c>
+      <c r="D142" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B143" s="9">
+        <v>135</v>
+      </c>
+      <c r="C143" s="9">
+        <v>33.75</v>
+      </c>
+      <c r="D143" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B144" s="9">
+        <v>136</v>
+      </c>
+      <c r="C144" s="9">
+        <v>34</v>
+      </c>
+      <c r="D144" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B145" s="9">
+        <v>137</v>
+      </c>
+      <c r="C145" s="9">
+        <v>34.25</v>
+      </c>
+      <c r="D145" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B146" s="9">
+        <v>138</v>
+      </c>
+      <c r="C146" s="9">
+        <v>34.5</v>
+      </c>
+      <c r="D146" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B147" s="9">
+        <v>139</v>
+      </c>
+      <c r="C147" s="9">
+        <v>34.75</v>
+      </c>
+      <c r="D147" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B148" s="9">
+        <v>140</v>
+      </c>
+      <c r="C148" s="9">
+        <v>35</v>
+      </c>
+      <c r="D148" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B149" s="9">
+        <v>141</v>
+      </c>
+      <c r="C149" s="9">
+        <v>35.25</v>
+      </c>
+      <c r="D149" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B150" s="9">
+        <v>142</v>
+      </c>
+      <c r="C150" s="9">
+        <v>35.5</v>
+      </c>
+      <c r="D150" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B151" s="9">
+        <v>143</v>
+      </c>
+      <c r="C151" s="9">
+        <v>35.75</v>
+      </c>
+      <c r="D151" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B152" s="9">
+        <v>144</v>
+      </c>
+      <c r="C152" s="9">
+        <v>36</v>
+      </c>
+      <c r="D152" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B153" s="9">
+        <v>145</v>
+      </c>
+      <c r="C153" s="9">
+        <v>36.25</v>
+      </c>
+      <c r="D153" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B154" s="9">
+        <v>146</v>
+      </c>
+      <c r="C154" s="9">
+        <v>36.5</v>
+      </c>
+      <c r="D154" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B155" s="9">
+        <v>147</v>
+      </c>
+      <c r="C155" s="9">
+        <v>36.75</v>
+      </c>
+      <c r="D155" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B156" s="9">
+        <v>148</v>
+      </c>
+      <c r="C156" s="9">
+        <v>37</v>
+      </c>
+      <c r="D156" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B157" s="9">
+        <v>149</v>
+      </c>
+      <c r="C157" s="9">
+        <v>37.25</v>
+      </c>
+      <c r="D157" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B158" s="9">
+        <v>150</v>
+      </c>
+      <c r="C158" s="9">
+        <v>37.5</v>
+      </c>
+      <c r="D158" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B159" s="9">
+        <v>151</v>
+      </c>
+      <c r="C159" s="9">
+        <v>37.75</v>
+      </c>
+      <c r="D159" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B160" s="9">
+        <v>152</v>
+      </c>
+      <c r="C160" s="9">
+        <v>38</v>
+      </c>
+      <c r="D160" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B161" s="9">
+        <v>153</v>
+      </c>
+      <c r="C161" s="9">
+        <v>38.25</v>
+      </c>
+      <c r="D161" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B162" s="9">
+        <v>154</v>
+      </c>
+      <c r="C162" s="9">
+        <v>38.5</v>
+      </c>
+      <c r="D162" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B163" s="9">
+        <v>155</v>
+      </c>
+      <c r="C163" s="9">
+        <v>38.75</v>
+      </c>
+      <c r="D163" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B164" s="9">
+        <v>156</v>
+      </c>
+      <c r="C164" s="9">
+        <v>39</v>
+      </c>
+      <c r="D164" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B165" s="9">
+        <v>157</v>
+      </c>
+      <c r="C165" s="9">
+        <v>39.25</v>
+      </c>
+      <c r="D165" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B166" s="9">
+        <v>158</v>
+      </c>
+      <c r="C166" s="9">
+        <v>39.5</v>
+      </c>
+      <c r="D166" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B167" s="9">
+        <v>159</v>
+      </c>
+      <c r="C167" s="9">
+        <v>39.75</v>
+      </c>
+      <c r="D167" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B168" s="9">
+        <v>160</v>
+      </c>
+      <c r="C168" s="9">
+        <v>40</v>
+      </c>
+      <c r="D168" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B169" s="9">
+        <v>161</v>
+      </c>
+      <c r="C169" s="9">
+        <v>40.25</v>
+      </c>
+      <c r="D169" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B170" s="9">
+        <v>162</v>
+      </c>
+      <c r="C170" s="9">
+        <v>40.5</v>
+      </c>
+      <c r="D170" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B171" s="9">
+        <v>163</v>
+      </c>
+      <c r="C171" s="9">
+        <v>40.75</v>
+      </c>
+      <c r="D171" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B172" s="9">
+        <v>164</v>
+      </c>
+      <c r="C172" s="9">
+        <v>41</v>
+      </c>
+      <c r="D172" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B173" s="9">
+        <v>165</v>
+      </c>
+      <c r="C173" s="9">
+        <v>41.25</v>
+      </c>
+      <c r="D173" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B174" s="9">
+        <v>166</v>
+      </c>
+      <c r="C174" s="9">
+        <v>41.5</v>
+      </c>
+      <c r="D174" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B175" s="9">
+        <v>167</v>
+      </c>
+      <c r="C175" s="9">
+        <v>41.75</v>
+      </c>
+      <c r="D175" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B176" s="9">
+        <v>168</v>
+      </c>
+      <c r="C176" s="9">
+        <v>42</v>
+      </c>
+      <c r="D176" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B177" s="9">
+        <v>169</v>
+      </c>
+      <c r="C177" s="9">
+        <v>42.25</v>
+      </c>
+      <c r="D177" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B178" s="9">
+        <v>170</v>
+      </c>
+      <c r="C178" s="9">
+        <v>42.5</v>
+      </c>
+      <c r="D178" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B179" s="9">
+        <v>171</v>
+      </c>
+      <c r="C179" s="9">
+        <v>42.75</v>
+      </c>
+      <c r="D179" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B180" s="9">
+        <v>172</v>
+      </c>
+      <c r="C180" s="9">
+        <v>43</v>
+      </c>
+      <c r="D180" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B181" s="9">
+        <v>173</v>
+      </c>
+      <c r="C181" s="9">
+        <v>43.25</v>
+      </c>
+      <c r="D181" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B182" s="9">
+        <v>174</v>
+      </c>
+      <c r="C182" s="9">
+        <v>43.5</v>
+      </c>
+      <c r="D182" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B183" s="9">
+        <v>175</v>
+      </c>
+      <c r="C183" s="9">
+        <v>43.75</v>
+      </c>
+      <c r="D183" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B184" s="9">
+        <v>176</v>
+      </c>
+      <c r="C184" s="9">
+        <v>44</v>
+      </c>
+      <c r="D184" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B185" s="9">
+        <v>177</v>
+      </c>
+      <c r="C185" s="9">
+        <v>44.25</v>
+      </c>
+      <c r="D185" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B186" s="9">
+        <v>178</v>
+      </c>
+      <c r="C186" s="9">
+        <v>44.5</v>
+      </c>
+      <c r="D186" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B187" s="9">
+        <v>179</v>
+      </c>
+      <c r="C187" s="9">
+        <v>44.75</v>
+      </c>
+      <c r="D187" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B188" s="9">
+        <v>180</v>
+      </c>
+      <c r="C188" s="9">
+        <v>45</v>
+      </c>
+      <c r="D188" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B189" s="9">
+        <v>181</v>
+      </c>
+      <c r="C189" s="9">
+        <v>45.25</v>
+      </c>
+      <c r="D189" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B190" s="9">
+        <v>182</v>
+      </c>
+      <c r="C190" s="9">
+        <v>45.5</v>
+      </c>
+      <c r="D190" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B191" s="9">
+        <v>183</v>
+      </c>
+      <c r="C191" s="9">
+        <v>45.75</v>
+      </c>
+      <c r="D191" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B192" s="9">
+        <v>184</v>
+      </c>
+      <c r="C192" s="9">
+        <v>46</v>
+      </c>
+      <c r="D192" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B193" s="9">
+        <v>185</v>
+      </c>
+      <c r="C193" s="9">
+        <v>46.25</v>
+      </c>
+      <c r="D193" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B194" s="9">
+        <v>186</v>
+      </c>
+      <c r="C194" s="9">
+        <v>46.5</v>
+      </c>
+      <c r="D194" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B195" s="9">
+        <v>187</v>
+      </c>
+      <c r="C195" s="9">
+        <v>46.75</v>
+      </c>
+      <c r="D195" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B196" s="9">
+        <v>188</v>
+      </c>
+      <c r="C196" s="9">
+        <v>47</v>
+      </c>
+      <c r="D196" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B197" s="9">
+        <v>189</v>
+      </c>
+      <c r="C197" s="9">
+        <v>47.25</v>
+      </c>
+      <c r="D197" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B198" s="9">
+        <v>190</v>
+      </c>
+      <c r="C198" s="9">
+        <v>47.5</v>
+      </c>
+      <c r="D198" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B199" s="9">
+        <v>191</v>
+      </c>
+      <c r="C199" s="9">
+        <v>47.75</v>
+      </c>
+      <c r="D199" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B200" s="9">
+        <v>192</v>
+      </c>
+      <c r="C200" s="9">
+        <v>48</v>
+      </c>
+      <c r="D200" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B201" s="9">
+        <v>193</v>
+      </c>
+      <c r="C201" s="9">
+        <v>48.25</v>
+      </c>
+      <c r="D201" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B202" s="9">
+        <v>194</v>
+      </c>
+      <c r="C202" s="9">
+        <v>48.5</v>
+      </c>
+      <c r="D202" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B203" s="9">
+        <v>195</v>
+      </c>
+      <c r="C203" s="9">
+        <v>48.75</v>
+      </c>
+      <c r="D203" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B204" s="9">
+        <v>196</v>
+      </c>
+      <c r="C204" s="9">
+        <v>49</v>
+      </c>
+      <c r="D204" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B205" s="9">
+        <v>197</v>
+      </c>
+      <c r="C205" s="9">
+        <v>49.25</v>
+      </c>
+      <c r="D205" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B206" s="9">
+        <v>198</v>
+      </c>
+      <c r="C206" s="9">
+        <v>49.5</v>
+      </c>
+      <c r="D206" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B207" s="9">
+        <v>199</v>
+      </c>
+      <c r="C207" s="9">
+        <v>49.75</v>
+      </c>
+      <c r="D207" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B208" s="9">
+        <v>200</v>
+      </c>
+      <c r="C208" s="9">
+        <v>50</v>
+      </c>
+      <c r="D208" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B209" s="9">
+        <v>201</v>
+      </c>
+      <c r="C209" s="9">
+        <v>50.25</v>
+      </c>
+      <c r="D209" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B210" s="9">
+        <v>202</v>
+      </c>
+      <c r="C210" s="9">
+        <v>50.5</v>
+      </c>
+      <c r="D210" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B211" s="9">
+        <v>203</v>
+      </c>
+      <c r="C211" s="9">
+        <v>50.75</v>
+      </c>
+      <c r="D211" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B212" s="9">
+        <v>204</v>
+      </c>
+      <c r="C212" s="9">
+        <v>51</v>
+      </c>
+      <c r="D212" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B213" s="9">
+        <v>205</v>
+      </c>
+      <c r="C213" s="9">
+        <v>51.25</v>
+      </c>
+      <c r="D213" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B214" s="9">
+        <v>206</v>
+      </c>
+      <c r="C214" s="9">
+        <v>51.5</v>
+      </c>
+      <c r="D214" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B215" s="9">
+        <v>207</v>
+      </c>
+      <c r="C215" s="9">
+        <v>51.75</v>
+      </c>
+      <c r="D215" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B216" s="9">
+        <v>208</v>
+      </c>
+      <c r="C216" s="9">
+        <v>52</v>
+      </c>
+      <c r="D216" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B217" s="9">
+        <v>209</v>
+      </c>
+      <c r="C217" s="9">
+        <v>52.25</v>
+      </c>
+      <c r="D217" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B218" s="9">
+        <v>210</v>
+      </c>
+      <c r="C218" s="9">
+        <v>52.5</v>
+      </c>
+      <c r="D218" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B219" s="9">
+        <v>211</v>
+      </c>
+      <c r="C219" s="9">
+        <v>52.75</v>
+      </c>
+      <c r="D219" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B220" s="9">
+        <v>212</v>
+      </c>
+      <c r="C220" s="9">
+        <v>53</v>
+      </c>
+      <c r="D220" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B221" s="9">
+        <v>213</v>
+      </c>
+      <c r="C221" s="9">
+        <v>53.25</v>
+      </c>
+      <c r="D221" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B222" s="9">
+        <v>214</v>
+      </c>
+      <c r="C222" s="9">
+        <v>53.5</v>
+      </c>
+      <c r="D222" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B223" s="9">
+        <v>215</v>
+      </c>
+      <c r="C223" s="9">
+        <v>53.75</v>
+      </c>
+      <c r="D223" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B224" s="9">
+        <v>216</v>
+      </c>
+      <c r="C224" s="9">
+        <v>54</v>
+      </c>
+      <c r="D224" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B225" s="9">
+        <v>217</v>
+      </c>
+      <c r="C225" s="9">
+        <v>54.25</v>
+      </c>
+      <c r="D225" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B226" s="9">
+        <v>218</v>
+      </c>
+      <c r="C226" s="9">
+        <v>54.5</v>
+      </c>
+      <c r="D226" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B227" s="9">
+        <v>219</v>
+      </c>
+      <c r="C227" s="9">
+        <v>54.75</v>
+      </c>
+      <c r="D227" s="9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="2:4" x14ac:dyDescent="0.5">
+      <c r="B228" s="9">
+        <v>220</v>
+      </c>
+      <c r="C228" s="9">
+        <v>55</v>
+      </c>
+      <c r="D228" s="9">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/file/table/BogotaRiverLevels_HECRAS_Parameters.xlsx
+++ b/file/table/BogotaRiverLevels_HECRAS_Parameters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.WREM\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3D845259-A5AE-4F93-89A8-160276FDBAF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{141DF1A8-00D7-4B53-B2CD-A32AD0FB9659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-93" yWindow="-93" windowWidth="20666" windowHeight="12266" firstSheet="2" activeTab="4" xr2:uid="{2255F479-0D41-4B39-BE5A-1B1436E09AAA}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="20666" windowHeight="12266" tabRatio="712" activeTab="4" xr2:uid="{2255F479-0D41-4B39-BE5A-1B1436E09AAA}"/>
   </bookViews>
   <sheets>
     <sheet name="21208110_21209770 " sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="59">
   <si>
     <t>Date</t>
   </si>
@@ -214,6 +214,9 @@
   </si>
   <si>
     <t>HEC-RAS 2D</t>
+  </si>
+  <si>
+    <t>Required Flow &gt;&gt;&gt;</t>
   </si>
 </sst>
 </file>
@@ -423,7 +426,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -503,6 +506,9 @@
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
   </cellXfs>
@@ -8717,21 +8723,22 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{150C82D4-B0A3-45ED-9F3F-D11EA85F382E}">
-  <dimension ref="B2:D228"/>
+  <dimension ref="B2:E230"/>
   <sheetFormatPr defaultRowHeight="16.350000000000001" x14ac:dyDescent="0.5"/>
   <cols>
     <col min="1" max="1" width="2.64453125" style="9" customWidth="1"/>
     <col min="2" max="3" width="17.76171875" style="9" customWidth="1"/>
-    <col min="4" max="4" width="16.234375" style="9" customWidth="1"/>
-    <col min="5" max="16384" width="8.9375" style="9"/>
+    <col min="4" max="4" width="17.1171875" style="9" customWidth="1"/>
+    <col min="5" max="5" width="15.5859375" style="9" customWidth="1"/>
+    <col min="6" max="16384" width="8.9375" style="9"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.5">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B2" s="9" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.5">
+    <row r="3" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B3" s="9" t="s">
         <v>49</v>
       </c>
@@ -8739,2455 +8746,3350 @@
         <v>250</v>
       </c>
     </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.5">
+    <row r="5" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B5" s="9" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.5">
+    <row r="6" spans="2:5" x14ac:dyDescent="0.5">
       <c r="B6" s="9" t="s">
         <v>56</v>
       </c>
     </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B7" s="9" t="s">
+    <row r="8" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="D8" s="9" t="s">
+        <v>58</v>
+      </c>
+      <c r="E8" s="29">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B9" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C9" s="9" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="9" t="s">
+      <c r="D9" s="9" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B8" s="9">
-        <v>0</v>
-      </c>
-      <c r="C8" s="9">
-        <v>0</v>
-      </c>
-      <c r="D8" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B9" s="9">
+      <c r="E9" s="9" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B10" s="9">
+        <v>0</v>
+      </c>
+      <c r="C10" s="9">
+        <v>0</v>
+      </c>
+      <c r="D10" s="9">
+        <v>0</v>
+      </c>
+      <c r="E10" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D10</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B11" s="9">
         <v>1</v>
       </c>
-      <c r="C9" s="9">
+      <c r="C11" s="9">
         <v>0.25</v>
       </c>
-      <c r="D9" s="9">
+      <c r="D11" s="9">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B10" s="9">
+      <c r="E11" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D11</f>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B12" s="9">
         <v>2</v>
       </c>
-      <c r="C10" s="9">
+      <c r="C12" s="9">
         <v>0.5</v>
       </c>
-      <c r="D10" s="9">
+      <c r="D12" s="9">
         <v>50</v>
       </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B11" s="9">
+      <c r="E12" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D12</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B13" s="9">
         <v>3</v>
       </c>
-      <c r="C11" s="9">
+      <c r="C13" s="9">
         <v>0.75</v>
       </c>
-      <c r="D11" s="9">
+      <c r="D13" s="9">
         <v>75</v>
       </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B12" s="9">
+      <c r="E13" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D13</f>
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B14" s="9">
         <v>4</v>
       </c>
-      <c r="C12" s="9">
+      <c r="C14" s="9">
         <v>1</v>
       </c>
-      <c r="D12" s="9">
+      <c r="D14" s="9">
         <v>100</v>
       </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B13" s="9">
+      <c r="E14" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D14</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B15" s="9">
         <v>5</v>
       </c>
-      <c r="C13" s="9">
+      <c r="C15" s="9">
         <v>1.25</v>
       </c>
-      <c r="D13" s="9">
+      <c r="D15" s="9">
         <v>87.5</v>
       </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B14" s="9">
+      <c r="E15" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D15</f>
+        <v>43.75</v>
+      </c>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B16" s="9">
         <v>6</v>
       </c>
-      <c r="C14" s="9">
+      <c r="C16" s="9">
         <v>1.5</v>
       </c>
-      <c r="D14" s="9">
+      <c r="D16" s="9">
         <v>75</v>
       </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B15" s="9">
+      <c r="E16" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D16</f>
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B17" s="9">
         <v>7</v>
       </c>
-      <c r="C15" s="9">
+      <c r="C17" s="9">
         <v>1.75</v>
       </c>
-      <c r="D15" s="9">
+      <c r="D17" s="9">
         <v>62.5</v>
       </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B16" s="9">
+      <c r="E17" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D17</f>
+        <v>31.25</v>
+      </c>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B18" s="9">
         <v>8</v>
       </c>
-      <c r="C16" s="9">
+      <c r="C18" s="9">
         <v>2</v>
       </c>
-      <c r="D16" s="9">
+      <c r="D18" s="9">
         <v>50</v>
       </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B17" s="9">
+      <c r="E18" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D18</f>
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B19" s="9">
         <v>9</v>
       </c>
-      <c r="C17" s="9">
+      <c r="C19" s="9">
         <v>2.25</v>
       </c>
-      <c r="D17" s="9">
+      <c r="D19" s="9">
         <v>37.5</v>
       </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B18" s="9">
+      <c r="E19" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D19</f>
+        <v>18.75</v>
+      </c>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B20" s="9">
         <v>10</v>
       </c>
-      <c r="C18" s="9">
+      <c r="C20" s="9">
         <v>2.5</v>
       </c>
-      <c r="D18" s="9">
+      <c r="D20" s="9">
         <v>25</v>
       </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B19" s="9">
+      <c r="E20" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D20</f>
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B21" s="9">
         <v>11</v>
       </c>
-      <c r="C19" s="9">
+      <c r="C21" s="9">
         <v>2.75</v>
       </c>
-      <c r="D19" s="9">
+      <c r="D21" s="9">
         <v>12.5</v>
       </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B20" s="9">
+      <c r="E21" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D21</f>
+        <v>6.25</v>
+      </c>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B22" s="9">
         <v>12</v>
       </c>
-      <c r="C20" s="9">
+      <c r="C22" s="9">
         <v>3</v>
       </c>
-      <c r="D20" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B21" s="9">
+      <c r="D22" s="9">
+        <v>0</v>
+      </c>
+      <c r="E22" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B23" s="9">
         <v>13</v>
       </c>
-      <c r="C21" s="9">
+      <c r="C23" s="9">
         <v>3.25</v>
       </c>
-      <c r="D21" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B22" s="9">
+      <c r="D23" s="9">
+        <v>0</v>
+      </c>
+      <c r="E23" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B24" s="9">
         <v>14</v>
       </c>
-      <c r="C22" s="9">
+      <c r="C24" s="9">
         <v>3.5</v>
       </c>
-      <c r="D22" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B23" s="9">
+      <c r="D24" s="9">
+        <v>0</v>
+      </c>
+      <c r="E24" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D24</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B25" s="9">
         <v>15</v>
       </c>
-      <c r="C23" s="9">
+      <c r="C25" s="9">
         <v>3.75</v>
       </c>
-      <c r="D23" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B24" s="9">
+      <c r="D25" s="9">
+        <v>0</v>
+      </c>
+      <c r="E25" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D25</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B26" s="9">
         <v>16</v>
       </c>
-      <c r="C24" s="9">
+      <c r="C26" s="9">
         <v>4</v>
       </c>
-      <c r="D24" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B25" s="9">
+      <c r="D26" s="9">
+        <v>0</v>
+      </c>
+      <c r="E26" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D26</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B27" s="9">
         <v>17</v>
       </c>
-      <c r="C25" s="9">
+      <c r="C27" s="9">
         <v>4.25</v>
       </c>
-      <c r="D25" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B26" s="9">
+      <c r="D27" s="9">
+        <v>0</v>
+      </c>
+      <c r="E27" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B28" s="9">
         <v>18</v>
       </c>
-      <c r="C26" s="9">
+      <c r="C28" s="9">
         <v>4.5</v>
       </c>
-      <c r="D26" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B27" s="9">
+      <c r="D28" s="9">
+        <v>0</v>
+      </c>
+      <c r="E28" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D28</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B29" s="9">
         <v>19</v>
       </c>
-      <c r="C27" s="9">
+      <c r="C29" s="9">
         <v>4.75</v>
       </c>
-      <c r="D27" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B28" s="9">
+      <c r="D29" s="9">
+        <v>0</v>
+      </c>
+      <c r="E29" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D29</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B30" s="9">
         <v>20</v>
       </c>
-      <c r="C28" s="9">
+      <c r="C30" s="9">
         <v>5</v>
       </c>
-      <c r="D28" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B29" s="9">
+      <c r="D30" s="9">
+        <v>0</v>
+      </c>
+      <c r="E30" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D30</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B31" s="9">
         <v>21</v>
       </c>
-      <c r="C29" s="9">
+      <c r="C31" s="9">
         <v>5.25</v>
       </c>
-      <c r="D29" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B30" s="9">
+      <c r="D31" s="9">
+        <v>0</v>
+      </c>
+      <c r="E31" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D31</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B32" s="9">
         <v>22</v>
       </c>
-      <c r="C30" s="9">
+      <c r="C32" s="9">
         <v>5.5</v>
       </c>
-      <c r="D30" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B31" s="9">
+      <c r="D32" s="9">
+        <v>0</v>
+      </c>
+      <c r="E32" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D32</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B33" s="9">
         <v>23</v>
       </c>
-      <c r="C31" s="9">
+      <c r="C33" s="9">
         <v>5.75</v>
       </c>
-      <c r="D31" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B32" s="9">
+      <c r="D33" s="9">
+        <v>0</v>
+      </c>
+      <c r="E33" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D33</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B34" s="9">
         <v>24</v>
       </c>
-      <c r="C32" s="9">
+      <c r="C34" s="9">
         <v>6</v>
       </c>
-      <c r="D32" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B33" s="9">
+      <c r="D34" s="9">
+        <v>0</v>
+      </c>
+      <c r="E34" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D34</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B35" s="9">
         <v>25</v>
       </c>
-      <c r="C33" s="9">
+      <c r="C35" s="9">
         <v>6.25</v>
       </c>
-      <c r="D33" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B34" s="9">
+      <c r="D35" s="9">
+        <v>0</v>
+      </c>
+      <c r="E35" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D35</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B36" s="9">
         <v>26</v>
       </c>
-      <c r="C34" s="9">
+      <c r="C36" s="9">
         <v>6.5</v>
       </c>
-      <c r="D34" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B35" s="9">
+      <c r="D36" s="9">
+        <v>0</v>
+      </c>
+      <c r="E36" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D36</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B37" s="9">
         <v>27</v>
       </c>
-      <c r="C35" s="9">
+      <c r="C37" s="9">
         <v>6.75</v>
       </c>
-      <c r="D35" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B36" s="9">
+      <c r="D37" s="9">
+        <v>0</v>
+      </c>
+      <c r="E37" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D37</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B38" s="9">
         <v>28</v>
       </c>
-      <c r="C36" s="9">
+      <c r="C38" s="9">
         <v>7</v>
       </c>
-      <c r="D36" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B37" s="9">
+      <c r="D38" s="9">
+        <v>0</v>
+      </c>
+      <c r="E38" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D38</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B39" s="9">
         <v>29</v>
       </c>
-      <c r="C37" s="9">
+      <c r="C39" s="9">
         <v>7.25</v>
       </c>
-      <c r="D37" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B38" s="9">
+      <c r="D39" s="9">
+        <v>0</v>
+      </c>
+      <c r="E39" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D39</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B40" s="9">
         <v>30</v>
       </c>
-      <c r="C38" s="9">
+      <c r="C40" s="9">
         <v>7.5</v>
       </c>
-      <c r="D38" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B39" s="9">
+      <c r="D40" s="9">
+        <v>0</v>
+      </c>
+      <c r="E40" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D40</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B41" s="9">
         <v>31</v>
       </c>
-      <c r="C39" s="9">
+      <c r="C41" s="9">
         <v>7.75</v>
       </c>
-      <c r="D39" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B40" s="9">
+      <c r="D41" s="9">
+        <v>0</v>
+      </c>
+      <c r="E41" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D41</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B42" s="9">
         <v>32</v>
       </c>
-      <c r="C40" s="9">
+      <c r="C42" s="9">
         <v>8</v>
       </c>
-      <c r="D40" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B41" s="9">
+      <c r="D42" s="9">
+        <v>0</v>
+      </c>
+      <c r="E42" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D42</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B43" s="9">
         <v>33</v>
       </c>
-      <c r="C41" s="9">
+      <c r="C43" s="9">
         <v>8.25</v>
       </c>
-      <c r="D41" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B42" s="9">
+      <c r="D43" s="9">
+        <v>0</v>
+      </c>
+      <c r="E43" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D43</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B44" s="9">
         <v>34</v>
       </c>
-      <c r="C42" s="9">
+      <c r="C44" s="9">
         <v>8.5</v>
       </c>
-      <c r="D42" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B43" s="9">
+      <c r="D44" s="9">
+        <v>0</v>
+      </c>
+      <c r="E44" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D44</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B45" s="9">
         <v>35</v>
       </c>
-      <c r="C43" s="9">
+      <c r="C45" s="9">
         <v>8.75</v>
       </c>
-      <c r="D43" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B44" s="9">
+      <c r="D45" s="9">
+        <v>0</v>
+      </c>
+      <c r="E45" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D45</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B46" s="9">
         <v>36</v>
       </c>
-      <c r="C44" s="9">
+      <c r="C46" s="9">
         <v>9</v>
       </c>
-      <c r="D44" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B45" s="9">
+      <c r="D46" s="9">
+        <v>0</v>
+      </c>
+      <c r="E46" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D46</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B47" s="9">
         <v>37</v>
       </c>
-      <c r="C45" s="9">
+      <c r="C47" s="9">
         <v>9.25</v>
       </c>
-      <c r="D45" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B46" s="9">
+      <c r="D47" s="9">
+        <v>0</v>
+      </c>
+      <c r="E47" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D47</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B48" s="9">
         <v>38</v>
       </c>
-      <c r="C46" s="9">
+      <c r="C48" s="9">
         <v>9.5</v>
       </c>
-      <c r="D46" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B47" s="9">
+      <c r="D48" s="9">
+        <v>0</v>
+      </c>
+      <c r="E48" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D48</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B49" s="9">
         <v>39</v>
       </c>
-      <c r="C47" s="9">
+      <c r="C49" s="9">
         <v>9.75</v>
       </c>
-      <c r="D47" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B48" s="9">
+      <c r="D49" s="9">
+        <v>0</v>
+      </c>
+      <c r="E49" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D49</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="50" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B50" s="9">
         <v>40</v>
       </c>
-      <c r="C48" s="9">
+      <c r="C50" s="9">
         <v>10</v>
       </c>
-      <c r="D48" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B49" s="9">
+      <c r="D50" s="9">
+        <v>0</v>
+      </c>
+      <c r="E50" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D50</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B51" s="9">
         <v>41</v>
       </c>
-      <c r="C49" s="9">
+      <c r="C51" s="9">
         <v>10.25</v>
       </c>
-      <c r="D49" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B50" s="9">
+      <c r="D51" s="9">
+        <v>0</v>
+      </c>
+      <c r="E51" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D51</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B52" s="9">
         <v>42</v>
       </c>
-      <c r="C50" s="9">
+      <c r="C52" s="9">
         <v>10.5</v>
       </c>
-      <c r="D50" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B51" s="9">
+      <c r="D52" s="9">
+        <v>0</v>
+      </c>
+      <c r="E52" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D52</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="53" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B53" s="9">
         <v>43</v>
       </c>
-      <c r="C51" s="9">
+      <c r="C53" s="9">
         <v>10.75</v>
       </c>
-      <c r="D51" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B52" s="9">
+      <c r="D53" s="9">
+        <v>0</v>
+      </c>
+      <c r="E53" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D53</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B54" s="9">
         <v>44</v>
       </c>
-      <c r="C52" s="9">
+      <c r="C54" s="9">
         <v>11</v>
       </c>
-      <c r="D52" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B53" s="9">
+      <c r="D54" s="9">
+        <v>0</v>
+      </c>
+      <c r="E54" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D54</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B55" s="9">
         <v>45</v>
       </c>
-      <c r="C53" s="9">
+      <c r="C55" s="9">
         <v>11.25</v>
       </c>
-      <c r="D53" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B54" s="9">
+      <c r="D55" s="9">
+        <v>0</v>
+      </c>
+      <c r="E55" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D55</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B56" s="9">
         <v>46</v>
       </c>
-      <c r="C54" s="9">
+      <c r="C56" s="9">
         <v>11.5</v>
       </c>
-      <c r="D54" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B55" s="9">
+      <c r="D56" s="9">
+        <v>0</v>
+      </c>
+      <c r="E56" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D56</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B57" s="9">
         <v>47</v>
       </c>
-      <c r="C55" s="9">
+      <c r="C57" s="9">
         <v>11.75</v>
       </c>
-      <c r="D55" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B56" s="9">
+      <c r="D57" s="9">
+        <v>0</v>
+      </c>
+      <c r="E57" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D57</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B58" s="9">
         <v>48</v>
       </c>
-      <c r="C56" s="9">
+      <c r="C58" s="9">
         <v>12</v>
       </c>
-      <c r="D56" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B57" s="9">
+      <c r="D58" s="9">
+        <v>0</v>
+      </c>
+      <c r="E58" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D58</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B59" s="9">
         <v>49</v>
       </c>
-      <c r="C57" s="9">
+      <c r="C59" s="9">
         <v>12.25</v>
       </c>
-      <c r="D57" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B58" s="9">
+      <c r="D59" s="9">
+        <v>0</v>
+      </c>
+      <c r="E59" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D59</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B60" s="9">
         <v>50</v>
       </c>
-      <c r="C58" s="9">
+      <c r="C60" s="9">
         <v>12.5</v>
       </c>
-      <c r="D58" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B59" s="9">
+      <c r="D60" s="9">
+        <v>0</v>
+      </c>
+      <c r="E60" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D60</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B61" s="9">
         <v>51</v>
       </c>
-      <c r="C59" s="9">
+      <c r="C61" s="9">
         <v>12.75</v>
       </c>
-      <c r="D59" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B60" s="9">
+      <c r="D61" s="9">
+        <v>0</v>
+      </c>
+      <c r="E61" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D61</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B62" s="9">
         <v>52</v>
       </c>
-      <c r="C60" s="9">
+      <c r="C62" s="9">
         <v>13</v>
       </c>
-      <c r="D60" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B61" s="9">
+      <c r="D62" s="9">
+        <v>0</v>
+      </c>
+      <c r="E62" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D62</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="63" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B63" s="9">
         <v>53</v>
       </c>
-      <c r="C61" s="9">
+      <c r="C63" s="9">
         <v>13.25</v>
       </c>
-      <c r="D61" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B62" s="9">
+      <c r="D63" s="9">
+        <v>0</v>
+      </c>
+      <c r="E63" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D63</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B64" s="9">
         <v>54</v>
       </c>
-      <c r="C62" s="9">
+      <c r="C64" s="9">
         <v>13.5</v>
       </c>
-      <c r="D62" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B63" s="9">
+      <c r="D64" s="9">
+        <v>0</v>
+      </c>
+      <c r="E64" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D64</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B65" s="9">
         <v>55</v>
       </c>
-      <c r="C63" s="9">
+      <c r="C65" s="9">
         <v>13.75</v>
       </c>
-      <c r="D63" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B64" s="9">
+      <c r="D65" s="9">
+        <v>0</v>
+      </c>
+      <c r="E65" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D65</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B66" s="9">
         <v>56</v>
       </c>
-      <c r="C64" s="9">
+      <c r="C66" s="9">
         <v>14</v>
       </c>
-      <c r="D64" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B65" s="9">
+      <c r="D66" s="9">
+        <v>0</v>
+      </c>
+      <c r="E66" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D66</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B67" s="9">
         <v>57</v>
       </c>
-      <c r="C65" s="9">
+      <c r="C67" s="9">
         <v>14.25</v>
       </c>
-      <c r="D65" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B66" s="9">
+      <c r="D67" s="9">
+        <v>0</v>
+      </c>
+      <c r="E67" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D67</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B68" s="9">
         <v>58</v>
       </c>
-      <c r="C66" s="9">
+      <c r="C68" s="9">
         <v>14.5</v>
       </c>
-      <c r="D66" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B67" s="9">
+      <c r="D68" s="9">
+        <v>0</v>
+      </c>
+      <c r="E68" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D68</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B69" s="9">
         <v>59</v>
       </c>
-      <c r="C67" s="9">
+      <c r="C69" s="9">
         <v>14.75</v>
       </c>
-      <c r="D67" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B68" s="9">
+      <c r="D69" s="9">
+        <v>0</v>
+      </c>
+      <c r="E69" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D69</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B70" s="9">
         <v>60</v>
       </c>
-      <c r="C68" s="9">
+      <c r="C70" s="9">
         <v>15</v>
       </c>
-      <c r="D68" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B69" s="9">
+      <c r="D70" s="9">
+        <v>0</v>
+      </c>
+      <c r="E70" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D70</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B71" s="9">
         <v>61</v>
       </c>
-      <c r="C69" s="9">
+      <c r="C71" s="9">
         <v>15.25</v>
       </c>
-      <c r="D69" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B70" s="9">
+      <c r="D71" s="9">
+        <v>0</v>
+      </c>
+      <c r="E71" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D71</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B72" s="9">
         <v>62</v>
       </c>
-      <c r="C70" s="9">
+      <c r="C72" s="9">
         <v>15.5</v>
       </c>
-      <c r="D70" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B71" s="9">
+      <c r="D72" s="9">
+        <v>0</v>
+      </c>
+      <c r="E72" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D72</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B73" s="9">
         <v>63</v>
       </c>
-      <c r="C71" s="9">
+      <c r="C73" s="9">
         <v>15.75</v>
       </c>
-      <c r="D71" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B72" s="9">
+      <c r="D73" s="9">
+        <v>0</v>
+      </c>
+      <c r="E73" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D73</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B74" s="9">
         <v>64</v>
       </c>
-      <c r="C72" s="9">
+      <c r="C74" s="9">
         <v>16</v>
       </c>
-      <c r="D72" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B73" s="9">
+      <c r="D74" s="9">
+        <v>0</v>
+      </c>
+      <c r="E74" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D74</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B75" s="9">
         <v>65</v>
       </c>
-      <c r="C73" s="9">
+      <c r="C75" s="9">
         <v>16.25</v>
       </c>
-      <c r="D73" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B74" s="9">
+      <c r="D75" s="9">
+        <v>0</v>
+      </c>
+      <c r="E75" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D75</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B76" s="9">
         <v>66</v>
       </c>
-      <c r="C74" s="9">
+      <c r="C76" s="9">
         <v>16.5</v>
       </c>
-      <c r="D74" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B75" s="9">
+      <c r="D76" s="9">
+        <v>0</v>
+      </c>
+      <c r="E76" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D76</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B77" s="9">
         <v>67</v>
       </c>
-      <c r="C75" s="9">
+      <c r="C77" s="9">
         <v>16.75</v>
       </c>
-      <c r="D75" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="76" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B76" s="9">
+      <c r="D77" s="9">
+        <v>0</v>
+      </c>
+      <c r="E77" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D77</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B78" s="9">
         <v>68</v>
       </c>
-      <c r="C76" s="9">
+      <c r="C78" s="9">
         <v>17</v>
       </c>
-      <c r="D76" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="77" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B77" s="9">
+      <c r="D78" s="9">
+        <v>0</v>
+      </c>
+      <c r="E78" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D78</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B79" s="9">
         <v>69</v>
       </c>
-      <c r="C77" s="9">
+      <c r="C79" s="9">
         <v>17.25</v>
       </c>
-      <c r="D77" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="78" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B78" s="9">
+      <c r="D79" s="9">
+        <v>0</v>
+      </c>
+      <c r="E79" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D79</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B80" s="9">
         <v>70</v>
       </c>
-      <c r="C78" s="9">
+      <c r="C80" s="9">
         <v>17.5</v>
       </c>
-      <c r="D78" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="79" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B79" s="9">
+      <c r="D80" s="9">
+        <v>0</v>
+      </c>
+      <c r="E80" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D80</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="81" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B81" s="9">
         <v>71</v>
       </c>
-      <c r="C79" s="9">
+      <c r="C81" s="9">
         <v>17.75</v>
       </c>
-      <c r="D79" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="80" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B80" s="9">
+      <c r="D81" s="9">
+        <v>0</v>
+      </c>
+      <c r="E81" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D81</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B82" s="9">
         <v>72</v>
       </c>
-      <c r="C80" s="9">
+      <c r="C82" s="9">
         <v>18</v>
       </c>
-      <c r="D80" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="81" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B81" s="9">
+      <c r="D82" s="9">
+        <v>0</v>
+      </c>
+      <c r="E82" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D82</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B83" s="9">
         <v>73</v>
       </c>
-      <c r="C81" s="9">
+      <c r="C83" s="9">
         <v>18.25</v>
       </c>
-      <c r="D81" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="82" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B82" s="9">
+      <c r="D83" s="9">
+        <v>0</v>
+      </c>
+      <c r="E83" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D83</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B84" s="9">
         <v>74</v>
       </c>
-      <c r="C82" s="9">
+      <c r="C84" s="9">
         <v>18.5</v>
       </c>
-      <c r="D82" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="83" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B83" s="9">
+      <c r="D84" s="9">
+        <v>0</v>
+      </c>
+      <c r="E84" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D84</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B85" s="9">
         <v>75</v>
       </c>
-      <c r="C83" s="9">
+      <c r="C85" s="9">
         <v>18.75</v>
       </c>
-      <c r="D83" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="84" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B84" s="9">
+      <c r="D85" s="9">
+        <v>0</v>
+      </c>
+      <c r="E85" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D85</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B86" s="9">
         <v>76</v>
       </c>
-      <c r="C84" s="9">
+      <c r="C86" s="9">
         <v>19</v>
       </c>
-      <c r="D84" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="85" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B85" s="9">
+      <c r="D86" s="9">
+        <v>0</v>
+      </c>
+      <c r="E86" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D86</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B87" s="9">
         <v>77</v>
       </c>
-      <c r="C85" s="9">
+      <c r="C87" s="9">
         <v>19.25</v>
       </c>
-      <c r="D85" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="86" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B86" s="9">
+      <c r="D87" s="9">
+        <v>0</v>
+      </c>
+      <c r="E87" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D87</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B88" s="9">
         <v>78</v>
       </c>
-      <c r="C86" s="9">
+      <c r="C88" s="9">
         <v>19.5</v>
       </c>
-      <c r="D86" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="87" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B87" s="9">
+      <c r="D88" s="9">
+        <v>0</v>
+      </c>
+      <c r="E88" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D88</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B89" s="9">
         <v>79</v>
       </c>
-      <c r="C87" s="9">
+      <c r="C89" s="9">
         <v>19.75</v>
       </c>
-      <c r="D87" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="88" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B88" s="9">
+      <c r="D89" s="9">
+        <v>0</v>
+      </c>
+      <c r="E89" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D89</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B90" s="9">
         <v>80</v>
       </c>
-      <c r="C88" s="9">
+      <c r="C90" s="9">
         <v>20</v>
       </c>
-      <c r="D88" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="89" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B89" s="9">
+      <c r="D90" s="9">
+        <v>0</v>
+      </c>
+      <c r="E90" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D90</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B91" s="9">
         <v>81</v>
       </c>
-      <c r="C89" s="9">
+      <c r="C91" s="9">
         <v>20.25</v>
       </c>
-      <c r="D89" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="90" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B90" s="9">
+      <c r="D91" s="9">
+        <v>0</v>
+      </c>
+      <c r="E91" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D91</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B92" s="9">
         <v>82</v>
       </c>
-      <c r="C90" s="9">
+      <c r="C92" s="9">
         <v>20.5</v>
       </c>
-      <c r="D90" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="91" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B91" s="9">
+      <c r="D92" s="9">
+        <v>0</v>
+      </c>
+      <c r="E92" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D92</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B93" s="9">
         <v>83</v>
       </c>
-      <c r="C91" s="9">
+      <c r="C93" s="9">
         <v>20.75</v>
       </c>
-      <c r="D91" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="92" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B92" s="9">
+      <c r="D93" s="9">
+        <v>0</v>
+      </c>
+      <c r="E93" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D93</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B94" s="9">
         <v>84</v>
       </c>
-      <c r="C92" s="9">
+      <c r="C94" s="9">
         <v>21</v>
       </c>
-      <c r="D92" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="93" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B93" s="9">
+      <c r="D94" s="9">
+        <v>0</v>
+      </c>
+      <c r="E94" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D94</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="95" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B95" s="9">
         <v>85</v>
       </c>
-      <c r="C93" s="9">
+      <c r="C95" s="9">
         <v>21.25</v>
       </c>
-      <c r="D93" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="94" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B94" s="9">
+      <c r="D95" s="9">
+        <v>0</v>
+      </c>
+      <c r="E95" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D95</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="96" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B96" s="9">
         <v>86</v>
       </c>
-      <c r="C94" s="9">
+      <c r="C96" s="9">
         <v>21.5</v>
       </c>
-      <c r="D94" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="95" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B95" s="9">
+      <c r="D96" s="9">
+        <v>0</v>
+      </c>
+      <c r="E96" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D96</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B97" s="9">
         <v>87</v>
       </c>
-      <c r="C95" s="9">
+      <c r="C97" s="9">
         <v>21.75</v>
       </c>
-      <c r="D95" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="96" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B96" s="9">
+      <c r="D97" s="9">
+        <v>0</v>
+      </c>
+      <c r="E97" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D97</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B98" s="9">
         <v>88</v>
       </c>
-      <c r="C96" s="9">
+      <c r="C98" s="9">
         <v>22</v>
       </c>
-      <c r="D96" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B97" s="9">
+      <c r="D98" s="9">
+        <v>0</v>
+      </c>
+      <c r="E98" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D98</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B99" s="9">
         <v>89</v>
       </c>
-      <c r="C97" s="9">
+      <c r="C99" s="9">
         <v>22.25</v>
       </c>
-      <c r="D97" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="98" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B98" s="9">
+      <c r="D99" s="9">
+        <v>0</v>
+      </c>
+      <c r="E99" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D99</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B100" s="9">
         <v>90</v>
       </c>
-      <c r="C98" s="9">
+      <c r="C100" s="9">
         <v>22.5</v>
       </c>
-      <c r="D98" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B99" s="9">
+      <c r="D100" s="9">
+        <v>0</v>
+      </c>
+      <c r="E100" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D100</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B101" s="9">
         <v>91</v>
       </c>
-      <c r="C99" s="9">
+      <c r="C101" s="9">
         <v>22.75</v>
       </c>
-      <c r="D99" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B100" s="9">
+      <c r="D101" s="9">
+        <v>0</v>
+      </c>
+      <c r="E101" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D101</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B102" s="9">
         <v>92</v>
       </c>
-      <c r="C100" s="9">
+      <c r="C102" s="9">
         <v>23</v>
       </c>
-      <c r="D100" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B101" s="9">
+      <c r="D102" s="9">
+        <v>0</v>
+      </c>
+      <c r="E102" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D102</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B103" s="9">
         <v>93</v>
       </c>
-      <c r="C101" s="9">
+      <c r="C103" s="9">
         <v>23.25</v>
       </c>
-      <c r="D101" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B102" s="9">
+      <c r="D103" s="9">
+        <v>0</v>
+      </c>
+      <c r="E103" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D103</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B104" s="9">
         <v>94</v>
       </c>
-      <c r="C102" s="9">
+      <c r="C104" s="9">
         <v>23.5</v>
       </c>
-      <c r="D102" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B103" s="9">
+      <c r="D104" s="9">
+        <v>0</v>
+      </c>
+      <c r="E104" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D104</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B105" s="9">
         <v>95</v>
       </c>
-      <c r="C103" s="9">
+      <c r="C105" s="9">
         <v>23.75</v>
       </c>
-      <c r="D103" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B104" s="9">
+      <c r="D105" s="9">
+        <v>0</v>
+      </c>
+      <c r="E105" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D105</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B106" s="9">
         <v>96</v>
       </c>
-      <c r="C104" s="9">
+      <c r="C106" s="9">
         <v>24</v>
       </c>
-      <c r="D104" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B105" s="9">
+      <c r="D106" s="9">
+        <v>0</v>
+      </c>
+      <c r="E106" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D106</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B107" s="9">
         <v>97</v>
       </c>
-      <c r="C105" s="9">
+      <c r="C107" s="9">
         <v>24.25</v>
       </c>
-      <c r="D105" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B106" s="9">
+      <c r="D107" s="9">
+        <v>0</v>
+      </c>
+      <c r="E107" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D107</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B108" s="9">
         <v>98</v>
       </c>
-      <c r="C106" s="9">
+      <c r="C108" s="9">
         <v>24.5</v>
       </c>
-      <c r="D106" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B107" s="9">
+      <c r="D108" s="9">
+        <v>0</v>
+      </c>
+      <c r="E108" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D108</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B109" s="9">
         <v>99</v>
       </c>
-      <c r="C107" s="9">
+      <c r="C109" s="9">
         <v>24.75</v>
       </c>
-      <c r="D107" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B108" s="9">
+      <c r="D109" s="9">
+        <v>0</v>
+      </c>
+      <c r="E109" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D109</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B110" s="9">
         <v>100</v>
       </c>
-      <c r="C108" s="9">
+      <c r="C110" s="9">
         <v>25</v>
       </c>
-      <c r="D108" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B109" s="9">
+      <c r="D110" s="9">
+        <v>0</v>
+      </c>
+      <c r="E110" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D110</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B111" s="9">
         <v>101</v>
       </c>
-      <c r="C109" s="9">
+      <c r="C111" s="9">
         <v>25.25</v>
       </c>
-      <c r="D109" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B110" s="9">
+      <c r="D111" s="9">
+        <v>0</v>
+      </c>
+      <c r="E111" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D111</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B112" s="9">
         <v>102</v>
       </c>
-      <c r="C110" s="9">
+      <c r="C112" s="9">
         <v>25.5</v>
       </c>
-      <c r="D110" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B111" s="9">
+      <c r="D112" s="9">
+        <v>0</v>
+      </c>
+      <c r="E112" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D112</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B113" s="9">
         <v>103</v>
       </c>
-      <c r="C111" s="9">
+      <c r="C113" s="9">
         <v>25.75</v>
       </c>
-      <c r="D111" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B112" s="9">
+      <c r="D113" s="9">
+        <v>0</v>
+      </c>
+      <c r="E113" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D113</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B114" s="9">
         <v>104</v>
       </c>
-      <c r="C112" s="9">
+      <c r="C114" s="9">
         <v>26</v>
       </c>
-      <c r="D112" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B113" s="9">
+      <c r="D114" s="9">
+        <v>0</v>
+      </c>
+      <c r="E114" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D114</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B115" s="9">
         <v>105</v>
       </c>
-      <c r="C113" s="9">
+      <c r="C115" s="9">
         <v>26.25</v>
       </c>
-      <c r="D113" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B114" s="9">
+      <c r="D115" s="9">
+        <v>0</v>
+      </c>
+      <c r="E115" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D115</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B116" s="9">
         <v>106</v>
       </c>
-      <c r="C114" s="9">
+      <c r="C116" s="9">
         <v>26.5</v>
       </c>
-      <c r="D114" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B115" s="9">
+      <c r="D116" s="9">
+        <v>0</v>
+      </c>
+      <c r="E116" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D116</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B117" s="9">
         <v>107</v>
       </c>
-      <c r="C115" s="9">
+      <c r="C117" s="9">
         <v>26.75</v>
       </c>
-      <c r="D115" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B116" s="9">
+      <c r="D117" s="9">
+        <v>0</v>
+      </c>
+      <c r="E117" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D117</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B118" s="9">
         <v>108</v>
       </c>
-      <c r="C116" s="9">
+      <c r="C118" s="9">
         <v>27</v>
       </c>
-      <c r="D116" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B117" s="9">
+      <c r="D118" s="9">
+        <v>0</v>
+      </c>
+      <c r="E118" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D118</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B119" s="9">
         <v>109</v>
       </c>
-      <c r="C117" s="9">
+      <c r="C119" s="9">
         <v>27.25</v>
       </c>
-      <c r="D117" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B118" s="9">
+      <c r="D119" s="9">
+        <v>0</v>
+      </c>
+      <c r="E119" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D119</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B120" s="9">
         <v>110</v>
       </c>
-      <c r="C118" s="9">
+      <c r="C120" s="9">
         <v>27.5</v>
       </c>
-      <c r="D118" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B119" s="9">
+      <c r="D120" s="9">
+        <v>0</v>
+      </c>
+      <c r="E120" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D120</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B121" s="9">
         <v>111</v>
       </c>
-      <c r="C119" s="9">
+      <c r="C121" s="9">
         <v>27.75</v>
       </c>
-      <c r="D119" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B120" s="9">
+      <c r="D121" s="9">
+        <v>0</v>
+      </c>
+      <c r="E121" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D121</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B122" s="9">
         <v>112</v>
       </c>
-      <c r="C120" s="9">
+      <c r="C122" s="9">
         <v>28</v>
       </c>
-      <c r="D120" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B121" s="9">
+      <c r="D122" s="9">
+        <v>0</v>
+      </c>
+      <c r="E122" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D122</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B123" s="9">
         <v>113</v>
       </c>
-      <c r="C121" s="9">
+      <c r="C123" s="9">
         <v>28.25</v>
       </c>
-      <c r="D121" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B122" s="9">
+      <c r="D123" s="9">
+        <v>0</v>
+      </c>
+      <c r="E123" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D123</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B124" s="9">
         <v>114</v>
       </c>
-      <c r="C122" s="9">
+      <c r="C124" s="9">
         <v>28.5</v>
       </c>
-      <c r="D122" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B123" s="9">
+      <c r="D124" s="9">
+        <v>0</v>
+      </c>
+      <c r="E124" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D124</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B125" s="9">
         <v>115</v>
       </c>
-      <c r="C123" s="9">
+      <c r="C125" s="9">
         <v>28.75</v>
       </c>
-      <c r="D123" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B124" s="9">
+      <c r="D125" s="9">
+        <v>0</v>
+      </c>
+      <c r="E125" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D125</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B126" s="9">
         <v>116</v>
       </c>
-      <c r="C124" s="9">
+      <c r="C126" s="9">
         <v>29</v>
       </c>
-      <c r="D124" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B125" s="9">
+      <c r="D126" s="9">
+        <v>0</v>
+      </c>
+      <c r="E126" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D126</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B127" s="9">
         <v>117</v>
       </c>
-      <c r="C125" s="9">
+      <c r="C127" s="9">
         <v>29.25</v>
       </c>
-      <c r="D125" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B126" s="9">
+      <c r="D127" s="9">
+        <v>0</v>
+      </c>
+      <c r="E127" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D127</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B128" s="9">
         <v>118</v>
       </c>
-      <c r="C126" s="9">
+      <c r="C128" s="9">
         <v>29.5</v>
       </c>
-      <c r="D126" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B127" s="9">
+      <c r="D128" s="9">
+        <v>0</v>
+      </c>
+      <c r="E128" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D128</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B129" s="9">
         <v>119</v>
       </c>
-      <c r="C127" s="9">
+      <c r="C129" s="9">
         <v>29.75</v>
       </c>
-      <c r="D127" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B128" s="9">
+      <c r="D129" s="9">
+        <v>0</v>
+      </c>
+      <c r="E129" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D129</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B130" s="9">
         <v>120</v>
       </c>
-      <c r="C128" s="9">
+      <c r="C130" s="9">
         <v>30</v>
       </c>
-      <c r="D128" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B129" s="9">
+      <c r="D130" s="9">
+        <v>0</v>
+      </c>
+      <c r="E130" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D130</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B131" s="9">
         <v>121</v>
       </c>
-      <c r="C129" s="9">
+      <c r="C131" s="9">
         <v>30.25</v>
       </c>
-      <c r="D129" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B130" s="9">
+      <c r="D131" s="9">
+        <v>0</v>
+      </c>
+      <c r="E131" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D131</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B132" s="9">
         <v>122</v>
       </c>
-      <c r="C130" s="9">
+      <c r="C132" s="9">
         <v>30.5</v>
       </c>
-      <c r="D130" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B131" s="9">
+      <c r="D132" s="9">
+        <v>0</v>
+      </c>
+      <c r="E132" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D132</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B133" s="9">
         <v>123</v>
       </c>
-      <c r="C131" s="9">
+      <c r="C133" s="9">
         <v>30.75</v>
       </c>
-      <c r="D131" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B132" s="9">
+      <c r="D133" s="9">
+        <v>0</v>
+      </c>
+      <c r="E133" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D133</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B134" s="9">
         <v>124</v>
       </c>
-      <c r="C132" s="9">
+      <c r="C134" s="9">
         <v>31</v>
       </c>
-      <c r="D132" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B133" s="9">
+      <c r="D134" s="9">
+        <v>0</v>
+      </c>
+      <c r="E134" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D134</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B135" s="9">
         <v>125</v>
       </c>
-      <c r="C133" s="9">
+      <c r="C135" s="9">
         <v>31.25</v>
       </c>
-      <c r="D133" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B134" s="9">
+      <c r="D135" s="9">
+        <v>0</v>
+      </c>
+      <c r="E135" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D135</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B136" s="9">
         <v>126</v>
       </c>
-      <c r="C134" s="9">
+      <c r="C136" s="9">
         <v>31.5</v>
       </c>
-      <c r="D134" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B135" s="9">
+      <c r="D136" s="9">
+        <v>0</v>
+      </c>
+      <c r="E136" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D136</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B137" s="9">
         <v>127</v>
       </c>
-      <c r="C135" s="9">
+      <c r="C137" s="9">
         <v>31.75</v>
       </c>
-      <c r="D135" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B136" s="9">
+      <c r="D137" s="9">
+        <v>0</v>
+      </c>
+      <c r="E137" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D137</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B138" s="9">
         <v>128</v>
       </c>
-      <c r="C136" s="9">
+      <c r="C138" s="9">
         <v>32</v>
       </c>
-      <c r="D136" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B137" s="9">
+      <c r="D138" s="9">
+        <v>0</v>
+      </c>
+      <c r="E138" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D138</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B139" s="9">
         <v>129</v>
       </c>
-      <c r="C137" s="9">
+      <c r="C139" s="9">
         <v>32.25</v>
       </c>
-      <c r="D137" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B138" s="9">
+      <c r="D139" s="9">
+        <v>0</v>
+      </c>
+      <c r="E139" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D139</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="140" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B140" s="9">
         <v>130</v>
       </c>
-      <c r="C138" s="9">
+      <c r="C140" s="9">
         <v>32.5</v>
       </c>
-      <c r="D138" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B139" s="9">
+      <c r="D140" s="9">
+        <v>0</v>
+      </c>
+      <c r="E140" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D140</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="141" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B141" s="9">
         <v>131</v>
       </c>
-      <c r="C139" s="9">
+      <c r="C141" s="9">
         <v>32.75</v>
       </c>
-      <c r="D139" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B140" s="9">
+      <c r="D141" s="9">
+        <v>0</v>
+      </c>
+      <c r="E141" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D141</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B142" s="9">
         <v>132</v>
       </c>
-      <c r="C140" s="9">
+      <c r="C142" s="9">
         <v>33</v>
       </c>
-      <c r="D140" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B141" s="9">
+      <c r="D142" s="9">
+        <v>0</v>
+      </c>
+      <c r="E142" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D142</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="143" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B143" s="9">
         <v>133</v>
       </c>
-      <c r="C141" s="9">
+      <c r="C143" s="9">
         <v>33.25</v>
       </c>
-      <c r="D141" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B142" s="9">
+      <c r="D143" s="9">
+        <v>0</v>
+      </c>
+      <c r="E143" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D143</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="144" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B144" s="9">
         <v>134</v>
       </c>
-      <c r="C142" s="9">
+      <c r="C144" s="9">
         <v>33.5</v>
       </c>
-      <c r="D142" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B143" s="9">
+      <c r="D144" s="9">
+        <v>0</v>
+      </c>
+      <c r="E144" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D144</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="145" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B145" s="9">
         <v>135</v>
       </c>
-      <c r="C143" s="9">
+      <c r="C145" s="9">
         <v>33.75</v>
       </c>
-      <c r="D143" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B144" s="9">
+      <c r="D145" s="9">
+        <v>0</v>
+      </c>
+      <c r="E145" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D145</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="146" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B146" s="9">
         <v>136</v>
       </c>
-      <c r="C144" s="9">
+      <c r="C146" s="9">
         <v>34</v>
       </c>
-      <c r="D144" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B145" s="9">
+      <c r="D146" s="9">
+        <v>0</v>
+      </c>
+      <c r="E146" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D146</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="147" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B147" s="9">
         <v>137</v>
       </c>
-      <c r="C145" s="9">
+      <c r="C147" s="9">
         <v>34.25</v>
       </c>
-      <c r="D145" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B146" s="9">
+      <c r="D147" s="9">
+        <v>0</v>
+      </c>
+      <c r="E147" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D147</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="148" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B148" s="9">
         <v>138</v>
       </c>
-      <c r="C146" s="9">
+      <c r="C148" s="9">
         <v>34.5</v>
       </c>
-      <c r="D146" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B147" s="9">
+      <c r="D148" s="9">
+        <v>0</v>
+      </c>
+      <c r="E148" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D148</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B149" s="9">
         <v>139</v>
       </c>
-      <c r="C147" s="9">
+      <c r="C149" s="9">
         <v>34.75</v>
       </c>
-      <c r="D147" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B148" s="9">
+      <c r="D149" s="9">
+        <v>0</v>
+      </c>
+      <c r="E149" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D149</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="150" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B150" s="9">
         <v>140</v>
       </c>
-      <c r="C148" s="9">
+      <c r="C150" s="9">
         <v>35</v>
       </c>
-      <c r="D148" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B149" s="9">
+      <c r="D150" s="9">
+        <v>0</v>
+      </c>
+      <c r="E150" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D150</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="151" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B151" s="9">
         <v>141</v>
       </c>
-      <c r="C149" s="9">
+      <c r="C151" s="9">
         <v>35.25</v>
       </c>
-      <c r="D149" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B150" s="9">
+      <c r="D151" s="9">
+        <v>0</v>
+      </c>
+      <c r="E151" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D151</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="152" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B152" s="9">
         <v>142</v>
       </c>
-      <c r="C150" s="9">
+      <c r="C152" s="9">
         <v>35.5</v>
       </c>
-      <c r="D150" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B151" s="9">
+      <c r="D152" s="9">
+        <v>0</v>
+      </c>
+      <c r="E152" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D152</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B153" s="9">
         <v>143</v>
       </c>
-      <c r="C151" s="9">
+      <c r="C153" s="9">
         <v>35.75</v>
       </c>
-      <c r="D151" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B152" s="9">
+      <c r="D153" s="9">
+        <v>0</v>
+      </c>
+      <c r="E153" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D153</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B154" s="9">
         <v>144</v>
       </c>
-      <c r="C152" s="9">
+      <c r="C154" s="9">
         <v>36</v>
       </c>
-      <c r="D152" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B153" s="9">
+      <c r="D154" s="9">
+        <v>0</v>
+      </c>
+      <c r="E154" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D154</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="155" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B155" s="9">
         <v>145</v>
       </c>
-      <c r="C153" s="9">
+      <c r="C155" s="9">
         <v>36.25</v>
       </c>
-      <c r="D153" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B154" s="9">
+      <c r="D155" s="9">
+        <v>0</v>
+      </c>
+      <c r="E155" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D155</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="156" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B156" s="9">
         <v>146</v>
       </c>
-      <c r="C154" s="9">
+      <c r="C156" s="9">
         <v>36.5</v>
       </c>
-      <c r="D154" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B155" s="9">
+      <c r="D156" s="9">
+        <v>0</v>
+      </c>
+      <c r="E156" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D156</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="157" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B157" s="9">
         <v>147</v>
       </c>
-      <c r="C155" s="9">
+      <c r="C157" s="9">
         <v>36.75</v>
       </c>
-      <c r="D155" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B156" s="9">
+      <c r="D157" s="9">
+        <v>0</v>
+      </c>
+      <c r="E157" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D157</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="158" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B158" s="9">
         <v>148</v>
       </c>
-      <c r="C156" s="9">
+      <c r="C158" s="9">
         <v>37</v>
       </c>
-      <c r="D156" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B157" s="9">
+      <c r="D158" s="9">
+        <v>0</v>
+      </c>
+      <c r="E158" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D158</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="159" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B159" s="9">
         <v>149</v>
       </c>
-      <c r="C157" s="9">
+      <c r="C159" s="9">
         <v>37.25</v>
       </c>
-      <c r="D157" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B158" s="9">
+      <c r="D159" s="9">
+        <v>0</v>
+      </c>
+      <c r="E159" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D159</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="160" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B160" s="9">
         <v>150</v>
       </c>
-      <c r="C158" s="9">
+      <c r="C160" s="9">
         <v>37.5</v>
       </c>
-      <c r="D158" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B159" s="9">
+      <c r="D160" s="9">
+        <v>0</v>
+      </c>
+      <c r="E160" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D160</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="161" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B161" s="9">
         <v>151</v>
       </c>
-      <c r="C159" s="9">
+      <c r="C161" s="9">
         <v>37.75</v>
       </c>
-      <c r="D159" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B160" s="9">
+      <c r="D161" s="9">
+        <v>0</v>
+      </c>
+      <c r="E161" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D161</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="162" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B162" s="9">
         <v>152</v>
       </c>
-      <c r="C160" s="9">
+      <c r="C162" s="9">
         <v>38</v>
       </c>
-      <c r="D160" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B161" s="9">
+      <c r="D162" s="9">
+        <v>0</v>
+      </c>
+      <c r="E162" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D162</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="163" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B163" s="9">
         <v>153</v>
       </c>
-      <c r="C161" s="9">
+      <c r="C163" s="9">
         <v>38.25</v>
       </c>
-      <c r="D161" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B162" s="9">
+      <c r="D163" s="9">
+        <v>0</v>
+      </c>
+      <c r="E163" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D163</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="164" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B164" s="9">
         <v>154</v>
       </c>
-      <c r="C162" s="9">
+      <c r="C164" s="9">
         <v>38.5</v>
       </c>
-      <c r="D162" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="163" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B163" s="9">
+      <c r="D164" s="9">
+        <v>0</v>
+      </c>
+      <c r="E164" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D164</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B165" s="9">
         <v>155</v>
       </c>
-      <c r="C163" s="9">
+      <c r="C165" s="9">
         <v>38.75</v>
       </c>
-      <c r="D163" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="164" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B164" s="9">
+      <c r="D165" s="9">
+        <v>0</v>
+      </c>
+      <c r="E165" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D165</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="166" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B166" s="9">
         <v>156</v>
       </c>
-      <c r="C164" s="9">
+      <c r="C166" s="9">
         <v>39</v>
       </c>
-      <c r="D164" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="165" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B165" s="9">
+      <c r="D166" s="9">
+        <v>0</v>
+      </c>
+      <c r="E166" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D166</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="167" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B167" s="9">
         <v>157</v>
       </c>
-      <c r="C165" s="9">
+      <c r="C167" s="9">
         <v>39.25</v>
       </c>
-      <c r="D165" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="166" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B166" s="9">
+      <c r="D167" s="9">
+        <v>0</v>
+      </c>
+      <c r="E167" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D167</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="168" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B168" s="9">
         <v>158</v>
       </c>
-      <c r="C166" s="9">
+      <c r="C168" s="9">
         <v>39.5</v>
       </c>
-      <c r="D166" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="167" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B167" s="9">
+      <c r="D168" s="9">
+        <v>0</v>
+      </c>
+      <c r="E168" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D168</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="169" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B169" s="9">
         <v>159</v>
       </c>
-      <c r="C167" s="9">
+      <c r="C169" s="9">
         <v>39.75</v>
       </c>
-      <c r="D167" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="168" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B168" s="9">
+      <c r="D169" s="9">
+        <v>0</v>
+      </c>
+      <c r="E169" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D169</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="170" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B170" s="9">
         <v>160</v>
       </c>
-      <c r="C168" s="9">
+      <c r="C170" s="9">
         <v>40</v>
       </c>
-      <c r="D168" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="169" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B169" s="9">
+      <c r="D170" s="9">
+        <v>0</v>
+      </c>
+      <c r="E170" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D170</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="171" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B171" s="9">
         <v>161</v>
       </c>
-      <c r="C169" s="9">
+      <c r="C171" s="9">
         <v>40.25</v>
       </c>
-      <c r="D169" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="170" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B170" s="9">
+      <c r="D171" s="9">
+        <v>0</v>
+      </c>
+      <c r="E171" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D171</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="172" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B172" s="9">
         <v>162</v>
       </c>
-      <c r="C170" s="9">
+      <c r="C172" s="9">
         <v>40.5</v>
       </c>
-      <c r="D170" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="171" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B171" s="9">
+      <c r="D172" s="9">
+        <v>0</v>
+      </c>
+      <c r="E172" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D172</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="173" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B173" s="9">
         <v>163</v>
       </c>
-      <c r="C171" s="9">
+      <c r="C173" s="9">
         <v>40.75</v>
       </c>
-      <c r="D171" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="172" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B172" s="9">
+      <c r="D173" s="9">
+        <v>0</v>
+      </c>
+      <c r="E173" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D173</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B174" s="9">
         <v>164</v>
       </c>
-      <c r="C172" s="9">
+      <c r="C174" s="9">
         <v>41</v>
       </c>
-      <c r="D172" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="173" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B173" s="9">
+      <c r="D174" s="9">
+        <v>0</v>
+      </c>
+      <c r="E174" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D174</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B175" s="9">
         <v>165</v>
       </c>
-      <c r="C173" s="9">
+      <c r="C175" s="9">
         <v>41.25</v>
       </c>
-      <c r="D173" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="174" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B174" s="9">
+      <c r="D175" s="9">
+        <v>0</v>
+      </c>
+      <c r="E175" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D175</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="176" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B176" s="9">
         <v>166</v>
       </c>
-      <c r="C174" s="9">
+      <c r="C176" s="9">
         <v>41.5</v>
       </c>
-      <c r="D174" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="175" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B175" s="9">
+      <c r="D176" s="9">
+        <v>0</v>
+      </c>
+      <c r="E176" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D176</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="177" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B177" s="9">
         <v>167</v>
       </c>
-      <c r="C175" s="9">
+      <c r="C177" s="9">
         <v>41.75</v>
       </c>
-      <c r="D175" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="176" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B176" s="9">
+      <c r="D177" s="9">
+        <v>0</v>
+      </c>
+      <c r="E177" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D177</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B178" s="9">
         <v>168</v>
       </c>
-      <c r="C176" s="9">
+      <c r="C178" s="9">
         <v>42</v>
       </c>
-      <c r="D176" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="177" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B177" s="9">
+      <c r="D178" s="9">
+        <v>0</v>
+      </c>
+      <c r="E178" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D178</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="179" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B179" s="9">
         <v>169</v>
       </c>
-      <c r="C177" s="9">
+      <c r="C179" s="9">
         <v>42.25</v>
       </c>
-      <c r="D177" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="178" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B178" s="9">
+      <c r="D179" s="9">
+        <v>0</v>
+      </c>
+      <c r="E179" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D179</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="180" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B180" s="9">
         <v>170</v>
       </c>
-      <c r="C178" s="9">
+      <c r="C180" s="9">
         <v>42.5</v>
       </c>
-      <c r="D178" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="179" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B179" s="9">
+      <c r="D180" s="9">
+        <v>0</v>
+      </c>
+      <c r="E180" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D180</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="181" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B181" s="9">
         <v>171</v>
       </c>
-      <c r="C179" s="9">
+      <c r="C181" s="9">
         <v>42.75</v>
       </c>
-      <c r="D179" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="180" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B180" s="9">
+      <c r="D181" s="9">
+        <v>0</v>
+      </c>
+      <c r="E181" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D181</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="182" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B182" s="9">
         <v>172</v>
       </c>
-      <c r="C180" s="9">
+      <c r="C182" s="9">
         <v>43</v>
       </c>
-      <c r="D180" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="181" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B181" s="9">
+      <c r="D182" s="9">
+        <v>0</v>
+      </c>
+      <c r="E182" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D182</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="183" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B183" s="9">
         <v>173</v>
       </c>
-      <c r="C181" s="9">
+      <c r="C183" s="9">
         <v>43.25</v>
       </c>
-      <c r="D181" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="182" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B182" s="9">
+      <c r="D183" s="9">
+        <v>0</v>
+      </c>
+      <c r="E183" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D183</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B184" s="9">
         <v>174</v>
       </c>
-      <c r="C182" s="9">
+      <c r="C184" s="9">
         <v>43.5</v>
       </c>
-      <c r="D182" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="183" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B183" s="9">
+      <c r="D184" s="9">
+        <v>0</v>
+      </c>
+      <c r="E184" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D184</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="185" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B185" s="9">
         <v>175</v>
       </c>
-      <c r="C183" s="9">
+      <c r="C185" s="9">
         <v>43.75</v>
       </c>
-      <c r="D183" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="184" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B184" s="9">
+      <c r="D185" s="9">
+        <v>0</v>
+      </c>
+      <c r="E185" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D185</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="186" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B186" s="9">
         <v>176</v>
       </c>
-      <c r="C184" s="9">
+      <c r="C186" s="9">
         <v>44</v>
       </c>
-      <c r="D184" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="185" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B185" s="9">
+      <c r="D186" s="9">
+        <v>0</v>
+      </c>
+      <c r="E186" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D186</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B187" s="9">
         <v>177</v>
       </c>
-      <c r="C185" s="9">
+      <c r="C187" s="9">
         <v>44.25</v>
       </c>
-      <c r="D185" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="186" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B186" s="9">
+      <c r="D187" s="9">
+        <v>0</v>
+      </c>
+      <c r="E187" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D187</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="188" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B188" s="9">
         <v>178</v>
       </c>
-      <c r="C186" s="9">
+      <c r="C188" s="9">
         <v>44.5</v>
       </c>
-      <c r="D186" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="187" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B187" s="9">
+      <c r="D188" s="9">
+        <v>0</v>
+      </c>
+      <c r="E188" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D188</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="189" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B189" s="9">
         <v>179</v>
       </c>
-      <c r="C187" s="9">
+      <c r="C189" s="9">
         <v>44.75</v>
       </c>
-      <c r="D187" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="188" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B188" s="9">
+      <c r="D189" s="9">
+        <v>0</v>
+      </c>
+      <c r="E189" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D189</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B190" s="9">
         <v>180</v>
       </c>
-      <c r="C188" s="9">
+      <c r="C190" s="9">
         <v>45</v>
       </c>
-      <c r="D188" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="189" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B189" s="9">
+      <c r="D190" s="9">
+        <v>0</v>
+      </c>
+      <c r="E190" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D190</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="191" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B191" s="9">
         <v>181</v>
       </c>
-      <c r="C189" s="9">
+      <c r="C191" s="9">
         <v>45.25</v>
       </c>
-      <c r="D189" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="190" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B190" s="9">
+      <c r="D191" s="9">
+        <v>0</v>
+      </c>
+      <c r="E191" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D191</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="192" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B192" s="9">
         <v>182</v>
       </c>
-      <c r="C190" s="9">
+      <c r="C192" s="9">
         <v>45.5</v>
       </c>
-      <c r="D190" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="191" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B191" s="9">
+      <c r="D192" s="9">
+        <v>0</v>
+      </c>
+      <c r="E192" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D192</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="193" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B193" s="9">
         <v>183</v>
       </c>
-      <c r="C191" s="9">
+      <c r="C193" s="9">
         <v>45.75</v>
       </c>
-      <c r="D191" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="192" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B192" s="9">
+      <c r="D193" s="9">
+        <v>0</v>
+      </c>
+      <c r="E193" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D193</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="194" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B194" s="9">
         <v>184</v>
       </c>
-      <c r="C192" s="9">
+      <c r="C194" s="9">
         <v>46</v>
       </c>
-      <c r="D192" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="193" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B193" s="9">
+      <c r="D194" s="9">
+        <v>0</v>
+      </c>
+      <c r="E194" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D194</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B195" s="9">
         <v>185</v>
       </c>
-      <c r="C193" s="9">
+      <c r="C195" s="9">
         <v>46.25</v>
       </c>
-      <c r="D193" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="194" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B194" s="9">
+      <c r="D195" s="9">
+        <v>0</v>
+      </c>
+      <c r="E195" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D195</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="196" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B196" s="9">
         <v>186</v>
       </c>
-      <c r="C194" s="9">
+      <c r="C196" s="9">
         <v>46.5</v>
       </c>
-      <c r="D194" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="195" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B195" s="9">
+      <c r="D196" s="9">
+        <v>0</v>
+      </c>
+      <c r="E196" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D196</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="197" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B197" s="9">
         <v>187</v>
       </c>
-      <c r="C195" s="9">
+      <c r="C197" s="9">
         <v>46.75</v>
       </c>
-      <c r="D195" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="196" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B196" s="9">
+      <c r="D197" s="9">
+        <v>0</v>
+      </c>
+      <c r="E197" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D197</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="198" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B198" s="9">
         <v>188</v>
       </c>
-      <c r="C196" s="9">
+      <c r="C198" s="9">
         <v>47</v>
       </c>
-      <c r="D196" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="197" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B197" s="9">
+      <c r="D198" s="9">
+        <v>0</v>
+      </c>
+      <c r="E198" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D198</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="199" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B199" s="9">
         <v>189</v>
       </c>
-      <c r="C197" s="9">
+      <c r="C199" s="9">
         <v>47.25</v>
       </c>
-      <c r="D197" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="198" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B198" s="9">
+      <c r="D199" s="9">
+        <v>0</v>
+      </c>
+      <c r="E199" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D199</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="200" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B200" s="9">
         <v>190</v>
       </c>
-      <c r="C198" s="9">
+      <c r="C200" s="9">
         <v>47.5</v>
       </c>
-      <c r="D198" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="199" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B199" s="9">
+      <c r="D200" s="9">
+        <v>0</v>
+      </c>
+      <c r="E200" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D200</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="201" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B201" s="9">
         <v>191</v>
       </c>
-      <c r="C199" s="9">
+      <c r="C201" s="9">
         <v>47.75</v>
       </c>
-      <c r="D199" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="200" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B200" s="9">
+      <c r="D201" s="9">
+        <v>0</v>
+      </c>
+      <c r="E201" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D201</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="202" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B202" s="9">
         <v>192</v>
       </c>
-      <c r="C200" s="9">
+      <c r="C202" s="9">
         <v>48</v>
       </c>
-      <c r="D200" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="201" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B201" s="9">
+      <c r="D202" s="9">
+        <v>0</v>
+      </c>
+      <c r="E202" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D202</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="203" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B203" s="9">
         <v>193</v>
       </c>
-      <c r="C201" s="9">
+      <c r="C203" s="9">
         <v>48.25</v>
       </c>
-      <c r="D201" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="202" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B202" s="9">
+      <c r="D203" s="9">
+        <v>0</v>
+      </c>
+      <c r="E203" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D203</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B204" s="9">
         <v>194</v>
       </c>
-      <c r="C202" s="9">
+      <c r="C204" s="9">
         <v>48.5</v>
       </c>
-      <c r="D202" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="203" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B203" s="9">
+      <c r="D204" s="9">
+        <v>0</v>
+      </c>
+      <c r="E204" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D204</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="205" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B205" s="9">
         <v>195</v>
       </c>
-      <c r="C203" s="9">
+      <c r="C205" s="9">
         <v>48.75</v>
       </c>
-      <c r="D203" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="204" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B204" s="9">
+      <c r="D205" s="9">
+        <v>0</v>
+      </c>
+      <c r="E205" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D205</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="206" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B206" s="9">
         <v>196</v>
       </c>
-      <c r="C204" s="9">
+      <c r="C206" s="9">
         <v>49</v>
       </c>
-      <c r="D204" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="205" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B205" s="9">
+      <c r="D206" s="9">
+        <v>0</v>
+      </c>
+      <c r="E206" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D206</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="207" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B207" s="9">
         <v>197</v>
       </c>
-      <c r="C205" s="9">
+      <c r="C207" s="9">
         <v>49.25</v>
       </c>
-      <c r="D205" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="206" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B206" s="9">
+      <c r="D207" s="9">
+        <v>0</v>
+      </c>
+      <c r="E207" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D207</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B208" s="9">
         <v>198</v>
       </c>
-      <c r="C206" s="9">
+      <c r="C208" s="9">
         <v>49.5</v>
       </c>
-      <c r="D206" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="207" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B207" s="9">
+      <c r="D208" s="9">
+        <v>0</v>
+      </c>
+      <c r="E208" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D208</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="209" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B209" s="9">
         <v>199</v>
       </c>
-      <c r="C207" s="9">
+      <c r="C209" s="9">
         <v>49.75</v>
       </c>
-      <c r="D207" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="208" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B208" s="9">
+      <c r="D209" s="9">
+        <v>0</v>
+      </c>
+      <c r="E209" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D209</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="210" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B210" s="9">
         <v>200</v>
       </c>
-      <c r="C208" s="9">
+      <c r="C210" s="9">
         <v>50</v>
       </c>
-      <c r="D208" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="209" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B209" s="9">
+      <c r="D210" s="9">
+        <v>0</v>
+      </c>
+      <c r="E210" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D210</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="211" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B211" s="9">
         <v>201</v>
       </c>
-      <c r="C209" s="9">
+      <c r="C211" s="9">
         <v>50.25</v>
       </c>
-      <c r="D209" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="210" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B210" s="9">
+      <c r="D211" s="9">
+        <v>0</v>
+      </c>
+      <c r="E211" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D211</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="212" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B212" s="9">
         <v>202</v>
       </c>
-      <c r="C210" s="9">
+      <c r="C212" s="9">
         <v>50.5</v>
       </c>
-      <c r="D210" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="211" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B211" s="9">
+      <c r="D212" s="9">
+        <v>0</v>
+      </c>
+      <c r="E212" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D212</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B213" s="9">
         <v>203</v>
       </c>
-      <c r="C211" s="9">
+      <c r="C213" s="9">
         <v>50.75</v>
       </c>
-      <c r="D211" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="212" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B212" s="9">
+      <c r="D213" s="9">
+        <v>0</v>
+      </c>
+      <c r="E213" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D213</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="214" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B214" s="9">
         <v>204</v>
       </c>
-      <c r="C212" s="9">
+      <c r="C214" s="9">
         <v>51</v>
       </c>
-      <c r="D212" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="213" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B213" s="9">
+      <c r="D214" s="9">
+        <v>0</v>
+      </c>
+      <c r="E214" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D214</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="215" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B215" s="9">
         <v>205</v>
       </c>
-      <c r="C213" s="9">
+      <c r="C215" s="9">
         <v>51.25</v>
       </c>
-      <c r="D213" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="214" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B214" s="9">
+      <c r="D215" s="9">
+        <v>0</v>
+      </c>
+      <c r="E215" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D215</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="216" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B216" s="9">
         <v>206</v>
       </c>
-      <c r="C214" s="9">
+      <c r="C216" s="9">
         <v>51.5</v>
       </c>
-      <c r="D214" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="215" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B215" s="9">
+      <c r="D216" s="9">
+        <v>0</v>
+      </c>
+      <c r="E216" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D216</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B217" s="9">
         <v>207</v>
       </c>
-      <c r="C215" s="9">
+      <c r="C217" s="9">
         <v>51.75</v>
       </c>
-      <c r="D215" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="216" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B216" s="9">
+      <c r="D217" s="9">
+        <v>0</v>
+      </c>
+      <c r="E217" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D217</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="218" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B218" s="9">
         <v>208</v>
       </c>
-      <c r="C216" s="9">
+      <c r="C218" s="9">
         <v>52</v>
       </c>
-      <c r="D216" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="217" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B217" s="9">
+      <c r="D218" s="9">
+        <v>0</v>
+      </c>
+      <c r="E218" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D218</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="219" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B219" s="9">
         <v>209</v>
       </c>
-      <c r="C217" s="9">
+      <c r="C219" s="9">
         <v>52.25</v>
       </c>
-      <c r="D217" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="218" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B218" s="9">
+      <c r="D219" s="9">
+        <v>0</v>
+      </c>
+      <c r="E219" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D219</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B220" s="9">
         <v>210</v>
       </c>
-      <c r="C218" s="9">
+      <c r="C220" s="9">
         <v>52.5</v>
       </c>
-      <c r="D218" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="219" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B219" s="9">
+      <c r="D220" s="9">
+        <v>0</v>
+      </c>
+      <c r="E220" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D220</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="221" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B221" s="9">
         <v>211</v>
       </c>
-      <c r="C219" s="9">
+      <c r="C221" s="9">
         <v>52.75</v>
       </c>
-      <c r="D219" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="220" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B220" s="9">
+      <c r="D221" s="9">
+        <v>0</v>
+      </c>
+      <c r="E221" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D221</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B222" s="9">
         <v>212</v>
       </c>
-      <c r="C220" s="9">
+      <c r="C222" s="9">
         <v>53</v>
       </c>
-      <c r="D220" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="221" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B221" s="9">
+      <c r="D222" s="9">
+        <v>0</v>
+      </c>
+      <c r="E222" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D222</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="223" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B223" s="9">
         <v>213</v>
       </c>
-      <c r="C221" s="9">
+      <c r="C223" s="9">
         <v>53.25</v>
       </c>
-      <c r="D221" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="222" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B222" s="9">
+      <c r="D223" s="9">
+        <v>0</v>
+      </c>
+      <c r="E223" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D223</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="224" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B224" s="9">
         <v>214</v>
       </c>
-      <c r="C222" s="9">
+      <c r="C224" s="9">
         <v>53.5</v>
       </c>
-      <c r="D222" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="223" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B223" s="9">
+      <c r="D224" s="9">
+        <v>0</v>
+      </c>
+      <c r="E224" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D224</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="225" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B225" s="9">
         <v>215</v>
       </c>
-      <c r="C223" s="9">
+      <c r="C225" s="9">
         <v>53.75</v>
       </c>
-      <c r="D223" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="224" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B224" s="9">
+      <c r="D225" s="9">
+        <v>0</v>
+      </c>
+      <c r="E225" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D225</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="226" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B226" s="9">
         <v>216</v>
       </c>
-      <c r="C224" s="9">
+      <c r="C226" s="9">
         <v>54</v>
       </c>
-      <c r="D224" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="225" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B225" s="9">
+      <c r="D226" s="9">
+        <v>0</v>
+      </c>
+      <c r="E226" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D226</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="227" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B227" s="9">
         <v>217</v>
       </c>
-      <c r="C225" s="9">
+      <c r="C227" s="9">
         <v>54.25</v>
       </c>
-      <c r="D225" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="226" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B226" s="9">
+      <c r="D227" s="9">
+        <v>0</v>
+      </c>
+      <c r="E227" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D227</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="228" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B228" s="9">
         <v>218</v>
       </c>
-      <c r="C226" s="9">
+      <c r="C228" s="9">
         <v>54.5</v>
       </c>
-      <c r="D226" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="227" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B227" s="9">
+      <c r="D228" s="9">
+        <v>0</v>
+      </c>
+      <c r="E228" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D228</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="229" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B229" s="9">
         <v>219</v>
       </c>
-      <c r="C227" s="9">
+      <c r="C229" s="9">
         <v>54.75</v>
       </c>
-      <c r="D227" s="9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="228" spans="2:4" x14ac:dyDescent="0.5">
-      <c r="B228" s="9">
+      <c r="D229" s="9">
+        <v>0</v>
+      </c>
+      <c r="E229" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D229</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="230" spans="2:5" x14ac:dyDescent="0.5">
+      <c r="B230" s="9">
         <v>220</v>
       </c>
-      <c r="C228" s="9">
+      <c r="C230" s="9">
         <v>55</v>
       </c>
-      <c r="D228" s="9">
+      <c r="D230" s="9">
+        <v>0</v>
+      </c>
+      <c r="E230" s="9">
+        <f>($E$8/MAX($D$10:$D$230))*D230</f>
         <v>0</v>
       </c>
     </row>

--- a/file/table/BogotaRiverLevels_HECRAS_Parameters.xlsx
+++ b/file/table/BogotaRiverLevels_HECRAS_Parameters.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30305"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30308"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\R.WREM\file\table\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{141DF1A8-00D7-4B53-B2CD-A32AD0FB9659}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{070954A0-CD59-4955-B08E-83F0FF10732A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-93" yWindow="-93" windowWidth="20666" windowHeight="12266" tabRatio="712" activeTab="4" xr2:uid="{2255F479-0D41-4B39-BE5A-1B1436E09AAA}"/>
   </bookViews>
@@ -8789,7 +8789,7 @@
         <v>0</v>
       </c>
       <c r="E10" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D10</f>
+        <f t="shared" ref="E10:E73" si="0">($E$8/MAX($D$10:$D$230))*D10</f>
         <v>0</v>
       </c>
     </row>
@@ -8804,7 +8804,7 @@
         <v>25</v>
       </c>
       <c r="E11" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D11</f>
+        <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
     </row>
@@ -8819,7 +8819,7 @@
         <v>50</v>
       </c>
       <c r="E12" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D12</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
     </row>
@@ -8834,7 +8834,7 @@
         <v>75</v>
       </c>
       <c r="E13" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D13</f>
+        <f t="shared" si="0"/>
         <v>37.5</v>
       </c>
     </row>
@@ -8849,7 +8849,7 @@
         <v>100</v>
       </c>
       <c r="E14" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D14</f>
+        <f t="shared" si="0"/>
         <v>50</v>
       </c>
     </row>
@@ -8864,7 +8864,7 @@
         <v>87.5</v>
       </c>
       <c r="E15" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D15</f>
+        <f t="shared" si="0"/>
         <v>43.75</v>
       </c>
     </row>
@@ -8879,7 +8879,7 @@
         <v>75</v>
       </c>
       <c r="E16" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D16</f>
+        <f t="shared" si="0"/>
         <v>37.5</v>
       </c>
     </row>
@@ -8894,7 +8894,7 @@
         <v>62.5</v>
       </c>
       <c r="E17" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D17</f>
+        <f t="shared" si="0"/>
         <v>31.25</v>
       </c>
     </row>
@@ -8909,7 +8909,7 @@
         <v>50</v>
       </c>
       <c r="E18" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D18</f>
+        <f t="shared" si="0"/>
         <v>25</v>
       </c>
     </row>
@@ -8924,7 +8924,7 @@
         <v>37.5</v>
       </c>
       <c r="E19" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D19</f>
+        <f t="shared" si="0"/>
         <v>18.75</v>
       </c>
     </row>
@@ -8939,7 +8939,7 @@
         <v>25</v>
       </c>
       <c r="E20" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D20</f>
+        <f t="shared" si="0"/>
         <v>12.5</v>
       </c>
     </row>
@@ -8954,7 +8954,7 @@
         <v>12.5</v>
       </c>
       <c r="E21" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D21</f>
+        <f t="shared" si="0"/>
         <v>6.25</v>
       </c>
     </row>
@@ -8969,7 +8969,7 @@
         <v>0</v>
       </c>
       <c r="E22" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D22</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -8984,7 +8984,7 @@
         <v>0</v>
       </c>
       <c r="E23" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D23</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -8999,7 +8999,7 @@
         <v>0</v>
       </c>
       <c r="E24" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D24</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9014,7 +9014,7 @@
         <v>0</v>
       </c>
       <c r="E25" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D25</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9029,7 +9029,7 @@
         <v>0</v>
       </c>
       <c r="E26" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D26</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9044,7 +9044,7 @@
         <v>0</v>
       </c>
       <c r="E27" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D27</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9059,7 +9059,7 @@
         <v>0</v>
       </c>
       <c r="E28" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D28</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9074,7 +9074,7 @@
         <v>0</v>
       </c>
       <c r="E29" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D29</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9089,7 +9089,7 @@
         <v>0</v>
       </c>
       <c r="E30" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D30</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9104,7 +9104,7 @@
         <v>0</v>
       </c>
       <c r="E31" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D31</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9119,7 +9119,7 @@
         <v>0</v>
       </c>
       <c r="E32" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D32</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9134,7 +9134,7 @@
         <v>0</v>
       </c>
       <c r="E33" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D33</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9149,7 +9149,7 @@
         <v>0</v>
       </c>
       <c r="E34" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D34</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9164,7 +9164,7 @@
         <v>0</v>
       </c>
       <c r="E35" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D35</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9179,7 +9179,7 @@
         <v>0</v>
       </c>
       <c r="E36" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D36</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9194,7 +9194,7 @@
         <v>0</v>
       </c>
       <c r="E37" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D37</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9209,7 +9209,7 @@
         <v>0</v>
       </c>
       <c r="E38" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D38</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
         <v>0</v>
       </c>
       <c r="E39" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D39</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9239,7 +9239,7 @@
         <v>0</v>
       </c>
       <c r="E40" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D40</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9254,7 +9254,7 @@
         <v>0</v>
       </c>
       <c r="E41" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D41</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9269,7 +9269,7 @@
         <v>0</v>
       </c>
       <c r="E42" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D42</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9284,7 +9284,7 @@
         <v>0</v>
       </c>
       <c r="E43" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D43</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9299,7 +9299,7 @@
         <v>0</v>
       </c>
       <c r="E44" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D44</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9314,7 +9314,7 @@
         <v>0</v>
       </c>
       <c r="E45" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D45</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9329,7 +9329,7 @@
         <v>0</v>
       </c>
       <c r="E46" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D46</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9344,7 +9344,7 @@
         <v>0</v>
       </c>
       <c r="E47" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D47</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9359,7 +9359,7 @@
         <v>0</v>
       </c>
       <c r="E48" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D48</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9374,7 +9374,7 @@
         <v>0</v>
       </c>
       <c r="E49" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D49</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9389,7 +9389,7 @@
         <v>0</v>
       </c>
       <c r="E50" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D50</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9404,7 +9404,7 @@
         <v>0</v>
       </c>
       <c r="E51" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D51</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9419,7 +9419,7 @@
         <v>0</v>
       </c>
       <c r="E52" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D52</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9434,7 +9434,7 @@
         <v>0</v>
       </c>
       <c r="E53" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D53</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9449,7 +9449,7 @@
         <v>0</v>
       </c>
       <c r="E54" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D54</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9464,7 +9464,7 @@
         <v>0</v>
       </c>
       <c r="E55" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D55</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9479,7 +9479,7 @@
         <v>0</v>
       </c>
       <c r="E56" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D56</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9494,7 +9494,7 @@
         <v>0</v>
       </c>
       <c r="E57" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D57</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9509,7 +9509,7 @@
         <v>0</v>
       </c>
       <c r="E58" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D58</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9524,7 +9524,7 @@
         <v>0</v>
       </c>
       <c r="E59" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D59</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9539,7 +9539,7 @@
         <v>0</v>
       </c>
       <c r="E60" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D60</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9554,7 +9554,7 @@
         <v>0</v>
       </c>
       <c r="E61" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D61</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9569,7 +9569,7 @@
         <v>0</v>
       </c>
       <c r="E62" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D62</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9584,7 +9584,7 @@
         <v>0</v>
       </c>
       <c r="E63" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D63</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9599,7 +9599,7 @@
         <v>0</v>
       </c>
       <c r="E64" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D64</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9614,7 +9614,7 @@
         <v>0</v>
       </c>
       <c r="E65" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D65</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9629,7 +9629,7 @@
         <v>0</v>
       </c>
       <c r="E66" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D66</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9644,7 +9644,7 @@
         <v>0</v>
       </c>
       <c r="E67" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D67</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9659,7 +9659,7 @@
         <v>0</v>
       </c>
       <c r="E68" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D68</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9674,7 +9674,7 @@
         <v>0</v>
       </c>
       <c r="E69" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D69</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9689,7 +9689,7 @@
         <v>0</v>
       </c>
       <c r="E70" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D70</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9704,7 +9704,7 @@
         <v>0</v>
       </c>
       <c r="E71" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D71</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9719,7 +9719,7 @@
         <v>0</v>
       </c>
       <c r="E72" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D72</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9734,7 +9734,7 @@
         <v>0</v>
       </c>
       <c r="E73" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D73</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -9749,7 +9749,7 @@
         <v>0</v>
       </c>
       <c r="E74" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D74</f>
+        <f t="shared" ref="E74:E137" si="1">($E$8/MAX($D$10:$D$230))*D74</f>
         <v>0</v>
       </c>
     </row>
@@ -9764,7 +9764,7 @@
         <v>0</v>
       </c>
       <c r="E75" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D75</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -9779,7 +9779,7 @@
         <v>0</v>
       </c>
       <c r="E76" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D76</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -9794,7 +9794,7 @@
         <v>0</v>
       </c>
       <c r="E77" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D77</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -9809,7 +9809,7 @@
         <v>0</v>
       </c>
       <c r="E78" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D78</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -9824,7 +9824,7 @@
         <v>0</v>
       </c>
       <c r="E79" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D79</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -9839,7 +9839,7 @@
         <v>0</v>
       </c>
       <c r="E80" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D80</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -9854,7 +9854,7 @@
         <v>0</v>
       </c>
       <c r="E81" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D81</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -9869,7 +9869,7 @@
         <v>0</v>
       </c>
       <c r="E82" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D82</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -9884,7 +9884,7 @@
         <v>0</v>
       </c>
       <c r="E83" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D83</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
         <v>0</v>
       </c>
       <c r="E84" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D84</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -9914,7 +9914,7 @@
         <v>0</v>
       </c>
       <c r="E85" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D85</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -9929,7 +9929,7 @@
         <v>0</v>
       </c>
       <c r="E86" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D86</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -9944,7 +9944,7 @@
         <v>0</v>
       </c>
       <c r="E87" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D87</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -9959,7 +9959,7 @@
         <v>0</v>
       </c>
       <c r="E88" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D88</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -9974,7 +9974,7 @@
         <v>0</v>
       </c>
       <c r="E89" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D89</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -9989,7 +9989,7 @@
         <v>0</v>
       </c>
       <c r="E90" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D90</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10004,7 +10004,7 @@
         <v>0</v>
       </c>
       <c r="E91" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D91</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10019,7 +10019,7 @@
         <v>0</v>
       </c>
       <c r="E92" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D92</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10034,7 +10034,7 @@
         <v>0</v>
       </c>
       <c r="E93" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D93</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10049,7 +10049,7 @@
         <v>0</v>
       </c>
       <c r="E94" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D94</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10064,7 +10064,7 @@
         <v>0</v>
       </c>
       <c r="E95" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D95</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10079,7 +10079,7 @@
         <v>0</v>
       </c>
       <c r="E96" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D96</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10094,7 +10094,7 @@
         <v>0</v>
       </c>
       <c r="E97" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D97</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10109,7 +10109,7 @@
         <v>0</v>
       </c>
       <c r="E98" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D98</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10124,7 +10124,7 @@
         <v>0</v>
       </c>
       <c r="E99" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D99</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10139,7 +10139,7 @@
         <v>0</v>
       </c>
       <c r="E100" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D100</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10154,7 +10154,7 @@
         <v>0</v>
       </c>
       <c r="E101" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D101</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10169,7 +10169,7 @@
         <v>0</v>
       </c>
       <c r="E102" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D102</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10184,7 +10184,7 @@
         <v>0</v>
       </c>
       <c r="E103" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D103</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10199,7 +10199,7 @@
         <v>0</v>
       </c>
       <c r="E104" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D104</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10214,7 +10214,7 @@
         <v>0</v>
       </c>
       <c r="E105" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D105</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10229,7 +10229,7 @@
         <v>0</v>
       </c>
       <c r="E106" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D106</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10244,7 +10244,7 @@
         <v>0</v>
       </c>
       <c r="E107" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D107</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10259,7 +10259,7 @@
         <v>0</v>
       </c>
       <c r="E108" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D108</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10274,7 +10274,7 @@
         <v>0</v>
       </c>
       <c r="E109" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D109</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10289,7 +10289,7 @@
         <v>0</v>
       </c>
       <c r="E110" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D110</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10304,7 +10304,7 @@
         <v>0</v>
       </c>
       <c r="E111" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D111</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10319,7 +10319,7 @@
         <v>0</v>
       </c>
       <c r="E112" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D112</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10334,7 +10334,7 @@
         <v>0</v>
       </c>
       <c r="E113" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D113</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10349,7 +10349,7 @@
         <v>0</v>
       </c>
       <c r="E114" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D114</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10364,7 +10364,7 @@
         <v>0</v>
       </c>
       <c r="E115" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D115</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
         <v>0</v>
       </c>
       <c r="E116" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D116</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10394,7 +10394,7 @@
         <v>0</v>
       </c>
       <c r="E117" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D117</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10409,7 +10409,7 @@
         <v>0</v>
       </c>
       <c r="E118" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D118</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10424,7 +10424,7 @@
         <v>0</v>
       </c>
       <c r="E119" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D119</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10439,7 +10439,7 @@
         <v>0</v>
       </c>
       <c r="E120" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D120</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10454,7 +10454,7 @@
         <v>0</v>
       </c>
       <c r="E121" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D121</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10469,7 +10469,7 @@
         <v>0</v>
       </c>
       <c r="E122" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D122</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10484,7 +10484,7 @@
         <v>0</v>
       </c>
       <c r="E123" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D123</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10499,7 +10499,7 @@
         <v>0</v>
       </c>
       <c r="E124" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D124</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10514,7 +10514,7 @@
         <v>0</v>
       </c>
       <c r="E125" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D125</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10529,7 +10529,7 @@
         <v>0</v>
       </c>
       <c r="E126" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D126</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10544,7 +10544,7 @@
         <v>0</v>
       </c>
       <c r="E127" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D127</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10559,7 +10559,7 @@
         <v>0</v>
       </c>
       <c r="E128" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D128</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10574,7 +10574,7 @@
         <v>0</v>
       </c>
       <c r="E129" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D129</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10589,7 +10589,7 @@
         <v>0</v>
       </c>
       <c r="E130" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D130</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10604,7 +10604,7 @@
         <v>0</v>
       </c>
       <c r="E131" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D131</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10619,7 +10619,7 @@
         <v>0</v>
       </c>
       <c r="E132" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D132</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10634,7 +10634,7 @@
         <v>0</v>
       </c>
       <c r="E133" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D133</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10649,7 +10649,7 @@
         <v>0</v>
       </c>
       <c r="E134" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D134</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10664,7 +10664,7 @@
         <v>0</v>
       </c>
       <c r="E135" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D135</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10679,7 +10679,7 @@
         <v>0</v>
       </c>
       <c r="E136" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D136</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10694,7 +10694,7 @@
         <v>0</v>
       </c>
       <c r="E137" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D137</f>
+        <f t="shared" si="1"/>
         <v>0</v>
       </c>
     </row>
@@ -10709,7 +10709,7 @@
         <v>0</v>
       </c>
       <c r="E138" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D138</f>
+        <f t="shared" ref="E138:E201" si="2">($E$8/MAX($D$10:$D$230))*D138</f>
         <v>0</v>
       </c>
     </row>
@@ -10724,7 +10724,7 @@
         <v>0</v>
       </c>
       <c r="E139" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D139</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -10739,7 +10739,7 @@
         <v>0</v>
       </c>
       <c r="E140" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D140</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -10754,7 +10754,7 @@
         <v>0</v>
       </c>
       <c r="E141" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D141</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -10769,7 +10769,7 @@
         <v>0</v>
       </c>
       <c r="E142" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D142</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -10784,7 +10784,7 @@
         <v>0</v>
       </c>
       <c r="E143" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D143</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -10799,7 +10799,7 @@
         <v>0</v>
       </c>
       <c r="E144" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D144</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -10814,7 +10814,7 @@
         <v>0</v>
       </c>
       <c r="E145" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D145</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -10829,7 +10829,7 @@
         <v>0</v>
       </c>
       <c r="E146" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D146</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -10844,7 +10844,7 @@
         <v>0</v>
       </c>
       <c r="E147" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D147</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -10859,7 +10859,7 @@
         <v>0</v>
       </c>
       <c r="E148" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D148</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -10874,7 +10874,7 @@
         <v>0</v>
       </c>
       <c r="E149" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D149</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -10889,7 +10889,7 @@
         <v>0</v>
       </c>
       <c r="E150" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D150</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -10904,7 +10904,7 @@
         <v>0</v>
       </c>
       <c r="E151" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D151</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -10919,7 +10919,7 @@
         <v>0</v>
       </c>
       <c r="E152" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D152</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -10934,7 +10934,7 @@
         <v>0</v>
       </c>
       <c r="E153" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D153</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -10949,7 +10949,7 @@
         <v>0</v>
       </c>
       <c r="E154" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D154</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -10964,7 +10964,7 @@
         <v>0</v>
       </c>
       <c r="E155" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D155</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -10979,7 +10979,7 @@
         <v>0</v>
       </c>
       <c r="E156" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D156</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -10994,7 +10994,7 @@
         <v>0</v>
       </c>
       <c r="E157" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D157</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
         <v>0</v>
       </c>
       <c r="E158" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D158</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11024,7 +11024,7 @@
         <v>0</v>
       </c>
       <c r="E159" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D159</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11039,7 +11039,7 @@
         <v>0</v>
       </c>
       <c r="E160" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D160</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11054,7 +11054,7 @@
         <v>0</v>
       </c>
       <c r="E161" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D161</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11069,7 +11069,7 @@
         <v>0</v>
       </c>
       <c r="E162" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D162</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11084,7 +11084,7 @@
         <v>0</v>
       </c>
       <c r="E163" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D163</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11099,7 +11099,7 @@
         <v>0</v>
       </c>
       <c r="E164" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D164</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11114,7 +11114,7 @@
         <v>0</v>
       </c>
       <c r="E165" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D165</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11129,7 +11129,7 @@
         <v>0</v>
       </c>
       <c r="E166" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D166</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11144,7 +11144,7 @@
         <v>0</v>
       </c>
       <c r="E167" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D167</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11159,7 +11159,7 @@
         <v>0</v>
       </c>
       <c r="E168" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D168</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11174,7 +11174,7 @@
         <v>0</v>
       </c>
       <c r="E169" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D169</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11189,7 +11189,7 @@
         <v>0</v>
       </c>
       <c r="E170" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D170</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11204,7 +11204,7 @@
         <v>0</v>
       </c>
       <c r="E171" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D171</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11219,7 +11219,7 @@
         <v>0</v>
       </c>
       <c r="E172" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D172</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11234,7 +11234,7 @@
         <v>0</v>
       </c>
       <c r="E173" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D173</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11249,7 +11249,7 @@
         <v>0</v>
       </c>
       <c r="E174" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D174</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11264,7 +11264,7 @@
         <v>0</v>
       </c>
       <c r="E175" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D175</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11279,7 +11279,7 @@
         <v>0</v>
       </c>
       <c r="E176" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D176</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11294,7 +11294,7 @@
         <v>0</v>
       </c>
       <c r="E177" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D177</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11309,7 +11309,7 @@
         <v>0</v>
       </c>
       <c r="E178" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D178</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11324,7 +11324,7 @@
         <v>0</v>
       </c>
       <c r="E179" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D179</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11339,7 +11339,7 @@
         <v>0</v>
       </c>
       <c r="E180" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D180</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11354,7 +11354,7 @@
         <v>0</v>
       </c>
       <c r="E181" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D181</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11369,7 +11369,7 @@
         <v>0</v>
       </c>
       <c r="E182" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D182</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11384,7 +11384,7 @@
         <v>0</v>
       </c>
       <c r="E183" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D183</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11399,7 +11399,7 @@
         <v>0</v>
       </c>
       <c r="E184" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D184</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11414,7 +11414,7 @@
         <v>0</v>
       </c>
       <c r="E185" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D185</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11429,7 +11429,7 @@
         <v>0</v>
       </c>
       <c r="E186" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D186</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11444,7 +11444,7 @@
         <v>0</v>
       </c>
       <c r="E187" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D187</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11459,7 +11459,7 @@
         <v>0</v>
       </c>
       <c r="E188" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D188</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11474,7 +11474,7 @@
         <v>0</v>
       </c>
       <c r="E189" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D189</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11489,7 +11489,7 @@
         <v>0</v>
       </c>
       <c r="E190" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D190</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11504,7 +11504,7 @@
         <v>0</v>
       </c>
       <c r="E191" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D191</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11519,7 +11519,7 @@
         <v>0</v>
       </c>
       <c r="E192" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D192</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11534,7 +11534,7 @@
         <v>0</v>
       </c>
       <c r="E193" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D193</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11549,7 +11549,7 @@
         <v>0</v>
       </c>
       <c r="E194" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D194</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11564,7 +11564,7 @@
         <v>0</v>
       </c>
       <c r="E195" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D195</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11579,7 +11579,7 @@
         <v>0</v>
       </c>
       <c r="E196" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D196</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11594,7 +11594,7 @@
         <v>0</v>
       </c>
       <c r="E197" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D197</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11609,7 +11609,7 @@
         <v>0</v>
       </c>
       <c r="E198" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D198</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11624,7 +11624,7 @@
         <v>0</v>
       </c>
       <c r="E199" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D199</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11639,7 +11639,7 @@
         <v>0</v>
       </c>
       <c r="E200" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D200</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11654,7 +11654,7 @@
         <v>0</v>
       </c>
       <c r="E201" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D201</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -11669,7 +11669,7 @@
         <v>0</v>
       </c>
       <c r="E202" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D202</f>
+        <f t="shared" ref="E202:E265" si="3">($E$8/MAX($D$10:$D$230))*D202</f>
         <v>0</v>
       </c>
     </row>
@@ -11684,7 +11684,7 @@
         <v>0</v>
       </c>
       <c r="E203" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D203</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11699,7 +11699,7 @@
         <v>0</v>
       </c>
       <c r="E204" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D204</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11714,7 +11714,7 @@
         <v>0</v>
       </c>
       <c r="E205" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D205</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11729,7 +11729,7 @@
         <v>0</v>
       </c>
       <c r="E206" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D206</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11744,7 +11744,7 @@
         <v>0</v>
       </c>
       <c r="E207" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D207</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11759,7 +11759,7 @@
         <v>0</v>
       </c>
       <c r="E208" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D208</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11774,7 +11774,7 @@
         <v>0</v>
       </c>
       <c r="E209" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D209</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11789,7 +11789,7 @@
         <v>0</v>
       </c>
       <c r="E210" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D210</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11804,7 +11804,7 @@
         <v>0</v>
       </c>
       <c r="E211" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D211</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11819,7 +11819,7 @@
         <v>0</v>
       </c>
       <c r="E212" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D212</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11834,7 +11834,7 @@
         <v>0</v>
       </c>
       <c r="E213" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D213</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11849,7 +11849,7 @@
         <v>0</v>
       </c>
       <c r="E214" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D214</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
         <v>0</v>
       </c>
       <c r="E215" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D215</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11879,7 +11879,7 @@
         <v>0</v>
       </c>
       <c r="E216" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D216</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11894,7 +11894,7 @@
         <v>0</v>
       </c>
       <c r="E217" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D217</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11909,7 +11909,7 @@
         <v>0</v>
       </c>
       <c r="E218" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D218</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11924,7 +11924,7 @@
         <v>0</v>
       </c>
       <c r="E219" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D219</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11939,7 +11939,7 @@
         <v>0</v>
       </c>
       <c r="E220" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D220</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11954,7 +11954,7 @@
         <v>0</v>
       </c>
       <c r="E221" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D221</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11969,7 +11969,7 @@
         <v>0</v>
       </c>
       <c r="E222" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D222</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11984,7 +11984,7 @@
         <v>0</v>
       </c>
       <c r="E223" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D223</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -11999,7 +11999,7 @@
         <v>0</v>
       </c>
       <c r="E224" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D224</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -12014,7 +12014,7 @@
         <v>0</v>
       </c>
       <c r="E225" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D225</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -12029,7 +12029,7 @@
         <v>0</v>
       </c>
       <c r="E226" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D226</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -12044,7 +12044,7 @@
         <v>0</v>
       </c>
       <c r="E227" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D227</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -12059,7 +12059,7 @@
         <v>0</v>
       </c>
       <c r="E228" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D228</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -12074,7 +12074,7 @@
         <v>0</v>
       </c>
       <c r="E229" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D229</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
@@ -12089,7 +12089,7 @@
         <v>0</v>
       </c>
       <c r="E230" s="9">
-        <f>($E$8/MAX($D$10:$D$230))*D230</f>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
     </row>
